--- a/api/1/clv2/xlsx/es/OrganisationRegistrationAgency.xlsx
+++ b/api/1/clv2/xlsx/es/OrganisationRegistrationAgency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="1379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="1383">
   <si>
     <t>code</t>
   </si>
@@ -892,6 +892,12 @@
     <t>https://gov-id-finder.codeforiati.org/countries/CO/</t>
   </si>
   <si>
+    <t>CO-CUIN</t>
+  </si>
+  <si>
+    <t>https://www.contaduria.gov.co/definicion-del-codigo-cuin</t>
+  </si>
+  <si>
     <t>CO-NIT</t>
   </si>
   <si>
@@ -1631,6 +1637,12 @@
   </si>
   <si>
     <t>https://gov-id-finder.codeforiati.org/countries/GW/</t>
+  </si>
+  <si>
+    <t>GW-NIF</t>
+  </si>
+  <si>
+    <t>https://kontaktu.mef.gw/</t>
   </si>
   <si>
     <t>GY-COA</t>
@@ -4495,7 +4507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E567"/>
+  <dimension ref="A1:E569"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -6563,7 +6575,7 @@
         <v>8</v>
       </c>
       <c r="E122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -6580,7 +6592,7 @@
         <v>8</v>
       </c>
       <c r="E123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -6588,10 +6600,10 @@
         <v>296</v>
       </c>
       <c r="B124" t="s">
+        <v>288</v>
+      </c>
+      <c r="C124" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="D124" t="s">
         <v>8</v>
@@ -6602,10 +6614,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
+        <v>298</v>
+      </c>
+      <c r="B125" t="s">
         <v>299</v>
-      </c>
-      <c r="B125" t="s">
-        <v>297</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>300</v>
@@ -6614,7 +6626,7 @@
         <v>8</v>
       </c>
       <c r="E125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -6622,27 +6634,27 @@
         <v>301</v>
       </c>
       <c r="B126" t="s">
+        <v>299</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="D126" t="s">
         <v>8</v>
       </c>
       <c r="E126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
+        <v>303</v>
+      </c>
+      <c r="B127" t="s">
         <v>304</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
@@ -6653,13 +6665,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
+        <v>306</v>
+      </c>
+      <c r="B128" t="s">
         <v>307</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="D128" t="s">
         <v>8</v>
@@ -6670,13 +6682,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
+        <v>309</v>
+      </c>
+      <c r="B129" t="s">
         <v>310</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="D129" t="s">
         <v>8</v>
@@ -6687,13 +6699,13 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
+        <v>312</v>
+      </c>
+      <c r="B130" t="s">
         <v>313</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="D130" t="s">
         <v>8</v>
@@ -6704,10 +6716,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
+        <v>315</v>
+      </c>
+      <c r="B131" t="s">
         <v>316</v>
-      </c>
-      <c r="B131" t="s">
-        <v>314</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>317</v>
@@ -6716,7 +6728,7 @@
         <v>8</v>
       </c>
       <c r="E131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -6724,24 +6736,24 @@
         <v>318</v>
       </c>
       <c r="B132" t="s">
+        <v>316</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="D132" t="s">
         <v>8</v>
       </c>
       <c r="E132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
+        <v>320</v>
+      </c>
+      <c r="B133" t="s">
         <v>321</v>
-      </c>
-      <c r="B133" t="s">
-        <v>319</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>322</v>
@@ -6750,7 +6762,7 @@
         <v>8</v>
       </c>
       <c r="E133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -6758,7 +6770,7 @@
         <v>323</v>
       </c>
       <c r="B134" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>324</v>
@@ -6767,7 +6779,7 @@
         <v>8</v>
       </c>
       <c r="E134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -6775,10 +6787,10 @@
         <v>325</v>
       </c>
       <c r="B135" t="s">
+        <v>321</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="D135" t="s">
         <v>8</v>
@@ -6789,10 +6801,10 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
+        <v>327</v>
+      </c>
+      <c r="B136" t="s">
         <v>328</v>
-      </c>
-      <c r="B136" t="s">
-        <v>326</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>329</v>
@@ -6801,7 +6813,7 @@
         <v>8</v>
       </c>
       <c r="E136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -6809,27 +6821,27 @@
         <v>330</v>
       </c>
       <c r="B137" t="s">
+        <v>328</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="D137" t="s">
         <v>8</v>
       </c>
       <c r="E137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
+        <v>332</v>
+      </c>
+      <c r="B138" t="s">
         <v>333</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="D138" t="s">
         <v>8</v>
@@ -6840,10 +6852,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
+        <v>335</v>
+      </c>
+      <c r="B139" t="s">
         <v>336</v>
-      </c>
-      <c r="B139" t="s">
-        <v>334</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>337</v>
@@ -6860,10 +6872,10 @@
         <v>338</v>
       </c>
       <c r="B140" t="s">
+        <v>336</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="D140" t="s">
         <v>8</v>
@@ -6874,13 +6886,13 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
+        <v>340</v>
+      </c>
+      <c r="B141" t="s">
         <v>341</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="D141" t="s">
         <v>8</v>
@@ -6891,13 +6903,13 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
+        <v>343</v>
+      </c>
+      <c r="B142" t="s">
         <v>344</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="D142" t="s">
         <v>8</v>
@@ -6908,13 +6920,13 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
+        <v>346</v>
+      </c>
+      <c r="B143" t="s">
         <v>347</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="D143" t="s">
         <v>8</v>
@@ -6925,10 +6937,10 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
+        <v>349</v>
+      </c>
+      <c r="B144" t="s">
         <v>350</v>
-      </c>
-      <c r="B144" t="s">
-        <v>348</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>351</v>
@@ -6937,7 +6949,7 @@
         <v>8</v>
       </c>
       <c r="E144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -6945,24 +6957,24 @@
         <v>352</v>
       </c>
       <c r="B145" t="s">
+        <v>350</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="D145" t="s">
         <v>8</v>
       </c>
       <c r="E145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
+        <v>354</v>
+      </c>
+      <c r="B146" t="s">
         <v>355</v>
-      </c>
-      <c r="B146" t="s">
-        <v>353</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>356</v>
@@ -6971,7 +6983,7 @@
         <v>8</v>
       </c>
       <c r="E146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -6979,27 +6991,27 @@
         <v>357</v>
       </c>
       <c r="B147" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D147" t="s">
         <v>8</v>
       </c>
       <c r="E147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
+        <v>359</v>
+      </c>
+      <c r="B148" t="s">
+        <v>355</v>
+      </c>
+      <c r="C148" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="B148" t="s">
-        <v>359</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>360</v>
       </c>
       <c r="D148" t="s">
         <v>8</v>
@@ -7010,10 +7022,10 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
+        <v>360</v>
+      </c>
+      <c r="B149" t="s">
         <v>361</v>
-      </c>
-      <c r="B149" t="s">
-        <v>359</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>362</v>
@@ -7022,7 +7034,7 @@
         <v>8</v>
       </c>
       <c r="E149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7030,7 +7042,7 @@
         <v>363</v>
       </c>
       <c r="B150" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>364</v>
@@ -7039,7 +7051,7 @@
         <v>8</v>
       </c>
       <c r="E150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -7047,10 +7059,10 @@
         <v>365</v>
       </c>
       <c r="B151" t="s">
+        <v>361</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="D151" t="s">
         <v>8</v>
@@ -7061,13 +7073,13 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
+        <v>367</v>
+      </c>
+      <c r="B152" t="s">
         <v>368</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="D152" t="s">
         <v>8</v>
@@ -7078,13 +7090,13 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
+        <v>370</v>
+      </c>
+      <c r="B153" t="s">
         <v>371</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="D153" t="s">
         <v>8</v>
@@ -7095,10 +7107,10 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
+        <v>373</v>
+      </c>
+      <c r="B154" t="s">
         <v>374</v>
-      </c>
-      <c r="B154" t="s">
-        <v>372</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>375</v>
@@ -7115,7 +7127,7 @@
         <v>376</v>
       </c>
       <c r="B155" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>377</v>
@@ -7124,7 +7136,7 @@
         <v>8</v>
       </c>
       <c r="E155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -7132,7 +7144,7 @@
         <v>378</v>
       </c>
       <c r="B156" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>379</v>
@@ -7141,7 +7153,7 @@
         <v>8</v>
       </c>
       <c r="E156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -7149,7 +7161,7 @@
         <v>380</v>
       </c>
       <c r="B157" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>381</v>
@@ -7158,7 +7170,7 @@
         <v>8</v>
       </c>
       <c r="E157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -7166,10 +7178,10 @@
         <v>382</v>
       </c>
       <c r="B158" t="s">
+        <v>374</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="D158" t="s">
         <v>8</v>
@@ -7180,10 +7192,10 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
+        <v>384</v>
+      </c>
+      <c r="B159" t="s">
         <v>385</v>
-      </c>
-      <c r="B159" t="s">
-        <v>383</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>386</v>
@@ -7192,7 +7204,7 @@
         <v>8</v>
       </c>
       <c r="E159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -7200,7 +7212,7 @@
         <v>387</v>
       </c>
       <c r="B160" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>388</v>
@@ -7217,7 +7229,7 @@
         <v>389</v>
       </c>
       <c r="B161" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>390</v>
@@ -7234,7 +7246,7 @@
         <v>391</v>
       </c>
       <c r="B162" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>392</v>
@@ -7243,7 +7255,7 @@
         <v>8</v>
       </c>
       <c r="E162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -7251,24 +7263,24 @@
         <v>393</v>
       </c>
       <c r="B163" t="s">
+        <v>385</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="D163" t="s">
         <v>8</v>
       </c>
       <c r="E163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
+        <v>395</v>
+      </c>
+      <c r="B164" t="s">
         <v>396</v>
-      </c>
-      <c r="B164" t="s">
-        <v>394</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>397</v>
@@ -7277,7 +7289,7 @@
         <v>8</v>
       </c>
       <c r="E164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -7285,7 +7297,7 @@
         <v>398</v>
       </c>
       <c r="B165" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>399</v>
@@ -7302,27 +7314,27 @@
         <v>400</v>
       </c>
       <c r="B166" t="s">
+        <v>396</v>
+      </c>
+      <c r="C166" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="D166" t="s">
         <v>8</v>
       </c>
       <c r="E166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
+        <v>402</v>
+      </c>
+      <c r="B167" t="s">
         <v>403</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C167" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="D167" t="s">
         <v>8</v>
@@ -7333,13 +7345,13 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
+        <v>405</v>
+      </c>
+      <c r="B168" t="s">
         <v>406</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C168" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>408</v>
       </c>
       <c r="D168" t="s">
         <v>8</v>
@@ -7350,13 +7362,13 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
+        <v>408</v>
+      </c>
+      <c r="B169" t="s">
         <v>409</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C169" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="D169" t="s">
         <v>8</v>
@@ -7367,13 +7379,13 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
+        <v>411</v>
+      </c>
+      <c r="B170" t="s">
         <v>412</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C170" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="D170" t="s">
         <v>8</v>
@@ -7384,16 +7396,16 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
+        <v>414</v>
+      </c>
+      <c r="B171" t="s">
         <v>415</v>
-      </c>
-      <c r="B171" t="s">
-        <v>413</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D171" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E171" t="b">
         <v>0</v>
@@ -7404,16 +7416,16 @@
         <v>417</v>
       </c>
       <c r="B172" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>418</v>
       </c>
       <c r="D172" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -7421,41 +7433,41 @@
         <v>419</v>
       </c>
       <c r="B173" t="s">
+        <v>415</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="D173" t="s">
         <v>8</v>
       </c>
       <c r="E173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
+        <v>421</v>
+      </c>
+      <c r="B174" t="s">
         <v>422</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="D174" t="s">
         <v>8</v>
       </c>
       <c r="E174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
+        <v>424</v>
+      </c>
+      <c r="B175" t="s">
         <v>425</v>
-      </c>
-      <c r="B175" t="s">
-        <v>423</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>426</v>
@@ -7472,7 +7484,7 @@
         <v>427</v>
       </c>
       <c r="B176" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>428</v>
@@ -7481,7 +7493,7 @@
         <v>8</v>
       </c>
       <c r="E176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -7489,7 +7501,7 @@
         <v>429</v>
       </c>
       <c r="B177" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>430</v>
@@ -7498,7 +7510,7 @@
         <v>8</v>
       </c>
       <c r="E177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -7506,7 +7518,7 @@
         <v>431</v>
       </c>
       <c r="B178" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>432</v>
@@ -7523,7 +7535,7 @@
         <v>433</v>
       </c>
       <c r="B179" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>434</v>
@@ -7540,7 +7552,7 @@
         <v>435</v>
       </c>
       <c r="B180" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>436</v>
@@ -7557,16 +7569,16 @@
         <v>437</v>
       </c>
       <c r="B181" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>438</v>
       </c>
       <c r="D181" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -7574,13 +7586,13 @@
         <v>439</v>
       </c>
       <c r="B182" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>440</v>
       </c>
       <c r="D182" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E182" t="b">
         <v>0</v>
@@ -7591,16 +7603,16 @@
         <v>441</v>
       </c>
       <c r="B183" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D183" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -7608,7 +7620,7 @@
         <v>443</v>
       </c>
       <c r="B184" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>444</v>
@@ -7625,7 +7637,7 @@
         <v>445</v>
       </c>
       <c r="B185" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>446</v>
@@ -7642,7 +7654,7 @@
         <v>447</v>
       </c>
       <c r="B186" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>448</v>
@@ -7659,7 +7671,7 @@
         <v>449</v>
       </c>
       <c r="B187" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>450</v>
@@ -7676,7 +7688,7 @@
         <v>451</v>
       </c>
       <c r="B188" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>452</v>
@@ -7693,7 +7705,7 @@
         <v>453</v>
       </c>
       <c r="B189" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>454</v>
@@ -7710,7 +7722,7 @@
         <v>455</v>
       </c>
       <c r="B190" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>456</v>
@@ -7727,7 +7739,7 @@
         <v>457</v>
       </c>
       <c r="B191" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>458</v>
@@ -7744,7 +7756,7 @@
         <v>459</v>
       </c>
       <c r="B192" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>460</v>
@@ -7753,7 +7765,7 @@
         <v>8</v>
       </c>
       <c r="E192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -7761,7 +7773,7 @@
         <v>461</v>
       </c>
       <c r="B193" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>462</v>
@@ -7778,7 +7790,7 @@
         <v>463</v>
       </c>
       <c r="B194" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>464</v>
@@ -7787,7 +7799,7 @@
         <v>8</v>
       </c>
       <c r="E194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -7795,7 +7807,7 @@
         <v>465</v>
       </c>
       <c r="B195" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>466</v>
@@ -7812,7 +7824,7 @@
         <v>467</v>
       </c>
       <c r="B196" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>468</v>
@@ -7829,7 +7841,7 @@
         <v>469</v>
       </c>
       <c r="B197" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>470</v>
@@ -7838,7 +7850,7 @@
         <v>8</v>
       </c>
       <c r="E197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -7846,7 +7858,7 @@
         <v>471</v>
       </c>
       <c r="B198" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>472</v>
@@ -7855,7 +7867,7 @@
         <v>8</v>
       </c>
       <c r="E198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -7863,27 +7875,27 @@
         <v>473</v>
       </c>
       <c r="B199" t="s">
+        <v>425</v>
+      </c>
+      <c r="C199" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="D199" t="s">
         <v>8</v>
       </c>
       <c r="E199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
+        <v>475</v>
+      </c>
+      <c r="B200" t="s">
         <v>476</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="D200" t="s">
         <v>8</v>
@@ -7894,10 +7906,10 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
+        <v>478</v>
+      </c>
+      <c r="B201" t="s">
         <v>479</v>
-      </c>
-      <c r="B201" t="s">
-        <v>477</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>480</v>
@@ -7914,7 +7926,7 @@
         <v>481</v>
       </c>
       <c r="B202" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>482</v>
@@ -7923,7 +7935,7 @@
         <v>8</v>
       </c>
       <c r="E202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -7931,27 +7943,27 @@
         <v>483</v>
       </c>
       <c r="B203" t="s">
+        <v>479</v>
+      </c>
+      <c r="C203" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="D203" t="s">
         <v>8</v>
       </c>
       <c r="E203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
+        <v>485</v>
+      </c>
+      <c r="B204" t="s">
         <v>486</v>
       </c>
-      <c r="B204" t="s">
+      <c r="C204" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="D204" t="s">
         <v>8</v>
@@ -7962,10 +7974,10 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
+        <v>488</v>
+      </c>
+      <c r="B205" t="s">
         <v>489</v>
-      </c>
-      <c r="B205" t="s">
-        <v>487</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>490</v>
@@ -7982,24 +7994,24 @@
         <v>491</v>
       </c>
       <c r="B206" t="s">
+        <v>489</v>
+      </c>
+      <c r="C206" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C206" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="D206" t="s">
         <v>8</v>
       </c>
       <c r="E206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
+        <v>493</v>
+      </c>
+      <c r="B207" t="s">
         <v>494</v>
-      </c>
-      <c r="B207" t="s">
-        <v>492</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>495</v>
@@ -8008,7 +8020,7 @@
         <v>8</v>
       </c>
       <c r="E207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -8016,7 +8028,7 @@
         <v>496</v>
       </c>
       <c r="B208" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>497</v>
@@ -8025,7 +8037,7 @@
         <v>8</v>
       </c>
       <c r="E208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -8033,7 +8045,7 @@
         <v>498</v>
       </c>
       <c r="B209" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>499</v>
@@ -8042,7 +8054,7 @@
         <v>8</v>
       </c>
       <c r="E209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -8050,10 +8062,10 @@
         <v>500</v>
       </c>
       <c r="B210" t="s">
+        <v>494</v>
+      </c>
+      <c r="C210" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="D210" t="s">
         <v>8</v>
@@ -8064,13 +8076,13 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
+        <v>502</v>
+      </c>
+      <c r="B211" t="s">
         <v>503</v>
       </c>
-      <c r="B211" t="s">
+      <c r="C211" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="D211" t="s">
         <v>8</v>
@@ -8081,30 +8093,30 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
+        <v>505</v>
+      </c>
+      <c r="B212" t="s">
         <v>506</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C212" s="1" t="s">
-        <v>508</v>
-      </c>
       <c r="D212" t="s">
         <v>8</v>
       </c>
       <c r="E212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
+        <v>508</v>
+      </c>
+      <c r="B213" t="s">
         <v>509</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C213" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="D213" t="s">
         <v>8</v>
@@ -8115,64 +8127,64 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
+        <v>511</v>
+      </c>
+      <c r="B214" t="s">
         <v>512</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="C214" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="D214" t="s">
         <v>8</v>
       </c>
       <c r="E214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
+        <v>514</v>
+      </c>
+      <c r="B215" t="s">
         <v>515</v>
       </c>
-      <c r="B215" t="s">
+      <c r="C215" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="C215" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="D215" t="s">
         <v>8</v>
       </c>
       <c r="E215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
+        <v>517</v>
+      </c>
+      <c r="B216" t="s">
         <v>518</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C216" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="D216" t="s">
         <v>8</v>
       </c>
       <c r="E216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
+        <v>520</v>
+      </c>
+      <c r="B217" t="s">
         <v>521</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C217" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="D217" t="s">
         <v>8</v>
@@ -8183,27 +8195,27 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
+        <v>523</v>
+      </c>
+      <c r="B218" t="s">
         <v>524</v>
       </c>
-      <c r="B218" t="s">
+      <c r="C218" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C218" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="D218" t="s">
         <v>8</v>
       </c>
       <c r="E218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
+        <v>526</v>
+      </c>
+      <c r="B219" t="s">
         <v>527</v>
-      </c>
-      <c r="B219" t="s">
-        <v>525</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>528</v>
@@ -8212,7 +8224,7 @@
         <v>8</v>
       </c>
       <c r="E219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -8220,7 +8232,7 @@
         <v>529</v>
       </c>
       <c r="B220" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>530</v>
@@ -8229,7 +8241,7 @@
         <v>8</v>
       </c>
       <c r="E220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -8237,7 +8249,7 @@
         <v>531</v>
       </c>
       <c r="B221" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>532</v>
@@ -8254,61 +8266,61 @@
         <v>533</v>
       </c>
       <c r="B222" t="s">
+        <v>527</v>
+      </c>
+      <c r="C222" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="D222" t="s">
         <v>8</v>
       </c>
       <c r="E222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" t="s">
+        <v>535</v>
+      </c>
+      <c r="B223" t="s">
         <v>536</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C223" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="D223" t="s">
         <v>8</v>
       </c>
       <c r="E223" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" t="s">
+        <v>538</v>
+      </c>
+      <c r="B224" t="s">
         <v>539</v>
       </c>
-      <c r="B224" t="s">
+      <c r="C224" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>541</v>
-      </c>
       <c r="D224" t="s">
         <v>8</v>
       </c>
       <c r="E224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
+        <v>541</v>
+      </c>
+      <c r="B225" t="s">
+        <v>539</v>
+      </c>
+      <c r="C225" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="B225" t="s">
-        <v>543</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="D225" t="s">
         <v>8</v>
@@ -8319,30 +8331,30 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
+        <v>543</v>
+      </c>
+      <c r="B226" t="s">
+        <v>544</v>
+      </c>
+      <c r="C226" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B226" t="s">
-        <v>543</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="D226" t="s">
         <v>8</v>
       </c>
       <c r="E226" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
+        <v>546</v>
+      </c>
+      <c r="B227" t="s">
         <v>547</v>
       </c>
-      <c r="B227" t="s">
+      <c r="C227" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="D227" t="s">
         <v>8</v>
@@ -8353,47 +8365,47 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
+        <v>549</v>
+      </c>
+      <c r="B228" t="s">
+        <v>547</v>
+      </c>
+      <c r="C228" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="B228" t="s">
-        <v>551</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="D228" t="s">
         <v>8</v>
       </c>
       <c r="E228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
+        <v>551</v>
+      </c>
+      <c r="B229" t="s">
+        <v>552</v>
+      </c>
+      <c r="C229" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B229" t="s">
-        <v>551</v>
-      </c>
-      <c r="C229" s="1" t="s">
-        <v>554</v>
-      </c>
       <c r="D229" t="s">
         <v>8</v>
       </c>
       <c r="E229" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" t="s">
+        <v>554</v>
+      </c>
+      <c r="B230" t="s">
         <v>555</v>
       </c>
-      <c r="B230" t="s">
+      <c r="C230" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="D230" t="s">
         <v>8</v>
@@ -8404,13 +8416,13 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
+        <v>557</v>
+      </c>
+      <c r="B231" t="s">
+        <v>555</v>
+      </c>
+      <c r="C231" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="B231" t="s">
-        <v>556</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>559</v>
       </c>
       <c r="D231" t="s">
         <v>8</v>
@@ -8421,10 +8433,10 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
+        <v>559</v>
+      </c>
+      <c r="B232" t="s">
         <v>560</v>
-      </c>
-      <c r="B232" t="s">
-        <v>556</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>561</v>
@@ -8433,7 +8445,7 @@
         <v>8</v>
       </c>
       <c r="E232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -8441,10 +8453,10 @@
         <v>562</v>
       </c>
       <c r="B233" t="s">
+        <v>560</v>
+      </c>
+      <c r="C233" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>564</v>
       </c>
       <c r="D233" t="s">
         <v>8</v>
@@ -8455,13 +8467,13 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" t="s">
+        <v>564</v>
+      </c>
+      <c r="B234" t="s">
+        <v>560</v>
+      </c>
+      <c r="C234" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="B234" t="s">
-        <v>566</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>567</v>
       </c>
       <c r="D234" t="s">
         <v>8</v>
@@ -8472,30 +8484,30 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
+        <v>566</v>
+      </c>
+      <c r="B235" t="s">
+        <v>567</v>
+      </c>
+      <c r="C235" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B235" t="s">
-        <v>566</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="D235" t="s">
         <v>8</v>
       </c>
       <c r="E235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
+        <v>569</v>
+      </c>
+      <c r="B236" t="s">
         <v>570</v>
       </c>
-      <c r="B236" t="s">
+      <c r="C236" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>572</v>
       </c>
       <c r="D236" t="s">
         <v>8</v>
@@ -8506,13 +8518,13 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
+        <v>572</v>
+      </c>
+      <c r="B237" t="s">
+        <v>570</v>
+      </c>
+      <c r="C237" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="B237" t="s">
-        <v>571</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>574</v>
       </c>
       <c r="D237" t="s">
         <v>8</v>
@@ -8523,19 +8535,19 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
+        <v>574</v>
+      </c>
+      <c r="B238" t="s">
         <v>575</v>
-      </c>
-      <c r="B238" t="s">
-        <v>571</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>576</v>
       </c>
       <c r="D238" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E238" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -8543,7 +8555,7 @@
         <v>577</v>
       </c>
       <c r="B239" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>578</v>
@@ -8560,13 +8572,13 @@
         <v>579</v>
       </c>
       <c r="B240" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>580</v>
       </c>
       <c r="D240" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E240" t="b">
         <v>0</v>
@@ -8577,13 +8589,13 @@
         <v>581</v>
       </c>
       <c r="B241" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>582</v>
       </c>
       <c r="D241" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E241" t="b">
         <v>0</v>
@@ -8594,7 +8606,7 @@
         <v>583</v>
       </c>
       <c r="B242" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>584</v>
@@ -8611,13 +8623,13 @@
         <v>585</v>
       </c>
       <c r="B243" t="s">
+        <v>575</v>
+      </c>
+      <c r="C243" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="C243" s="1" t="s">
-        <v>587</v>
-      </c>
       <c r="D243" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E243" t="b">
         <v>0</v>
@@ -8625,13 +8637,13 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" t="s">
+        <v>587</v>
+      </c>
+      <c r="B244" t="s">
+        <v>575</v>
+      </c>
+      <c r="C244" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="B244" t="s">
-        <v>586</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="D244" t="s">
         <v>8</v>
@@ -8642,10 +8654,10 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
+        <v>589</v>
+      </c>
+      <c r="B245" t="s">
         <v>590</v>
-      </c>
-      <c r="B245" t="s">
-        <v>586</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>591</v>
@@ -8662,10 +8674,10 @@
         <v>592</v>
       </c>
       <c r="B246" t="s">
+        <v>590</v>
+      </c>
+      <c r="C246" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="D246" t="s">
         <v>8</v>
@@ -8676,27 +8688,27 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" t="s">
+        <v>594</v>
+      </c>
+      <c r="B247" t="s">
+        <v>590</v>
+      </c>
+      <c r="C247" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B247" t="s">
-        <v>593</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="D247" t="s">
         <v>8</v>
       </c>
       <c r="E247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" t="s">
+        <v>596</v>
+      </c>
+      <c r="B248" t="s">
         <v>597</v>
-      </c>
-      <c r="B248" t="s">
-        <v>593</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>598</v>
@@ -8705,7 +8717,7 @@
         <v>8</v>
       </c>
       <c r="E248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -8713,41 +8725,41 @@
         <v>599</v>
       </c>
       <c r="B249" t="s">
+        <v>597</v>
+      </c>
+      <c r="C249" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="C249" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="D249" t="s">
         <v>8</v>
       </c>
       <c r="E249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" t="s">
+        <v>601</v>
+      </c>
+      <c r="B250" t="s">
+        <v>597</v>
+      </c>
+      <c r="C250" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="B250" t="s">
-        <v>600</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="D250" t="s">
         <v>8</v>
       </c>
       <c r="E250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" t="s">
+        <v>603</v>
+      </c>
+      <c r="B251" t="s">
         <v>604</v>
-      </c>
-      <c r="B251" t="s">
-        <v>600</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>605</v>
@@ -8756,7 +8768,7 @@
         <v>8</v>
       </c>
       <c r="E251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -8764,10 +8776,10 @@
         <v>606</v>
       </c>
       <c r="B252" t="s">
+        <v>604</v>
+      </c>
+      <c r="C252" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>608</v>
       </c>
       <c r="D252" t="s">
         <v>8</v>
@@ -8778,13 +8790,13 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
+        <v>608</v>
+      </c>
+      <c r="B253" t="s">
+        <v>604</v>
+      </c>
+      <c r="C253" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="B253" t="s">
-        <v>607</v>
-      </c>
-      <c r="C253" s="1" t="s">
-        <v>610</v>
       </c>
       <c r="D253" t="s">
         <v>8</v>
@@ -8795,10 +8807,10 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
+        <v>610</v>
+      </c>
+      <c r="B254" t="s">
         <v>611</v>
-      </c>
-      <c r="B254" t="s">
-        <v>607</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>612</v>
@@ -8815,7 +8827,7 @@
         <v>613</v>
       </c>
       <c r="B255" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>614</v>
@@ -8824,7 +8836,7 @@
         <v>8</v>
       </c>
       <c r="E255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -8832,10 +8844,10 @@
         <v>615</v>
       </c>
       <c r="B256" t="s">
+        <v>611</v>
+      </c>
+      <c r="C256" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>617</v>
       </c>
       <c r="D256" t="s">
         <v>8</v>
@@ -8846,13 +8858,13 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
+        <v>617</v>
+      </c>
+      <c r="B257" t="s">
+        <v>611</v>
+      </c>
+      <c r="C257" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="B257" t="s">
-        <v>619</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>620</v>
       </c>
       <c r="D257" t="s">
         <v>8</v>
@@ -8863,27 +8875,27 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" t="s">
+        <v>619</v>
+      </c>
+      <c r="B258" t="s">
+        <v>620</v>
+      </c>
+      <c r="C258" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B258" t="s">
-        <v>619</v>
-      </c>
-      <c r="C258" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="D258" t="s">
         <v>8</v>
       </c>
       <c r="E258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
+        <v>622</v>
+      </c>
+      <c r="B259" t="s">
         <v>623</v>
-      </c>
-      <c r="B259" t="s">
-        <v>619</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>624</v>
@@ -8900,27 +8912,27 @@
         <v>625</v>
       </c>
       <c r="B260" t="s">
+        <v>623</v>
+      </c>
+      <c r="C260" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="C260" s="1" t="s">
-        <v>627</v>
-      </c>
       <c r="D260" t="s">
         <v>8</v>
       </c>
       <c r="E260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
+        <v>627</v>
+      </c>
+      <c r="B261" t="s">
+        <v>623</v>
+      </c>
+      <c r="C261" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="B261" t="s">
-        <v>629</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>630</v>
       </c>
       <c r="D261" t="s">
         <v>8</v>
@@ -8931,61 +8943,61 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" t="s">
+        <v>629</v>
+      </c>
+      <c r="B262" t="s">
+        <v>630</v>
+      </c>
+      <c r="C262" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B262" t="s">
-        <v>629</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="D262" t="s">
         <v>8</v>
       </c>
       <c r="E262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
+        <v>632</v>
+      </c>
+      <c r="B263" t="s">
         <v>633</v>
       </c>
-      <c r="B263" t="s">
+      <c r="C263" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="C263" s="1" t="s">
-        <v>635</v>
-      </c>
       <c r="D263" t="s">
         <v>8</v>
       </c>
       <c r="E263" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" t="s">
+        <v>635</v>
+      </c>
+      <c r="B264" t="s">
+        <v>633</v>
+      </c>
+      <c r="C264" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B264" t="s">
-        <v>634</v>
-      </c>
-      <c r="C264" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="D264" t="s">
         <v>8</v>
       </c>
       <c r="E264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" t="s">
+        <v>637</v>
+      </c>
+      <c r="B265" t="s">
         <v>638</v>
-      </c>
-      <c r="B265" t="s">
-        <v>634</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>639</v>
@@ -9002,24 +9014,24 @@
         <v>640</v>
       </c>
       <c r="B266" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D266" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E266" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B267" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>643</v>
@@ -9028,7 +9040,7 @@
         <v>8</v>
       </c>
       <c r="E267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -9036,24 +9048,24 @@
         <v>644</v>
       </c>
       <c r="B268" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="D268" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:5">
       <c r="A269" t="s">
+        <v>645</v>
+      </c>
+      <c r="B269" t="s">
         <v>646</v>
-      </c>
-      <c r="B269" t="s">
-        <v>642</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>647</v>
@@ -9062,7 +9074,7 @@
         <v>8</v>
       </c>
       <c r="E269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -9070,13 +9082,13 @@
         <v>648</v>
       </c>
       <c r="B270" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>649</v>
       </c>
       <c r="D270" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E270" t="b">
         <v>0</v>
@@ -9087,10 +9099,10 @@
         <v>650</v>
       </c>
       <c r="B271" t="s">
+        <v>646</v>
+      </c>
+      <c r="C271" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>652</v>
       </c>
       <c r="D271" t="s">
         <v>8</v>
@@ -9101,30 +9113,30 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" t="s">
+        <v>652</v>
+      </c>
+      <c r="B272" t="s">
+        <v>646</v>
+      </c>
+      <c r="C272" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B272" t="s">
-        <v>654</v>
-      </c>
-      <c r="C272" s="1" t="s">
-        <v>655</v>
-      </c>
       <c r="D272" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273" spans="1:5">
       <c r="A273" t="s">
+        <v>654</v>
+      </c>
+      <c r="B273" t="s">
+        <v>655</v>
+      </c>
+      <c r="C273" s="1" t="s">
         <v>656</v>
-      </c>
-      <c r="B273" t="s">
-        <v>654</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>657</v>
       </c>
       <c r="D273" t="s">
         <v>8</v>
@@ -9135,10 +9147,10 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" t="s">
+        <v>657</v>
+      </c>
+      <c r="B274" t="s">
         <v>658</v>
-      </c>
-      <c r="B274" t="s">
-        <v>654</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>659</v>
@@ -9155,27 +9167,27 @@
         <v>660</v>
       </c>
       <c r="B275" t="s">
+        <v>658</v>
+      </c>
+      <c r="C275" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C275" s="1" t="s">
-        <v>662</v>
-      </c>
       <c r="D275" t="s">
         <v>8</v>
       </c>
       <c r="E275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" t="s">
+        <v>662</v>
+      </c>
+      <c r="B276" t="s">
+        <v>658</v>
+      </c>
+      <c r="C276" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="B276" t="s">
-        <v>661</v>
-      </c>
-      <c r="C276" s="1" t="s">
-        <v>664</v>
       </c>
       <c r="D276" t="s">
         <v>8</v>
@@ -9186,44 +9198,44 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" t="s">
+        <v>664</v>
+      </c>
+      <c r="B277" t="s">
         <v>665</v>
       </c>
-      <c r="B277" t="s">
+      <c r="C277" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="C277" s="1" t="s">
-        <v>667</v>
-      </c>
       <c r="D277" t="s">
         <v>8</v>
       </c>
       <c r="E277" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278" spans="1:5">
       <c r="A278" t="s">
+        <v>667</v>
+      </c>
+      <c r="B278" t="s">
+        <v>665</v>
+      </c>
+      <c r="C278" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B278" t="s">
-        <v>666</v>
-      </c>
-      <c r="C278" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="D278" t="s">
         <v>8</v>
       </c>
       <c r="E278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:5">
       <c r="A279" t="s">
+        <v>669</v>
+      </c>
+      <c r="B279" t="s">
         <v>670</v>
-      </c>
-      <c r="B279" t="s">
-        <v>666</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>671</v>
@@ -9232,7 +9244,7 @@
         <v>8</v>
       </c>
       <c r="E279" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -9240,7 +9252,7 @@
         <v>672</v>
       </c>
       <c r="B280" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>673</v>
@@ -9257,13 +9269,13 @@
         <v>674</v>
       </c>
       <c r="B281" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D281" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E281" t="b">
         <v>0</v>
@@ -9271,10 +9283,10 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B282" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>677</v>
@@ -9291,24 +9303,24 @@
         <v>678</v>
       </c>
       <c r="B283" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D283" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E283" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284" spans="1:5">
       <c r="A284" t="s">
+        <v>679</v>
+      </c>
+      <c r="B284" t="s">
         <v>680</v>
-      </c>
-      <c r="B284" t="s">
-        <v>676</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>681</v>
@@ -9317,7 +9329,7 @@
         <v>8</v>
       </c>
       <c r="E284" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -9325,7 +9337,7 @@
         <v>682</v>
       </c>
       <c r="B285" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>683</v>
@@ -9342,10 +9354,10 @@
         <v>684</v>
       </c>
       <c r="B286" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D286" t="s">
         <v>8</v>
@@ -9356,10 +9368,10 @@
     </row>
     <row r="287" spans="1:5">
       <c r="A287" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B287" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>687</v>
@@ -9368,7 +9380,7 @@
         <v>8</v>
       </c>
       <c r="E287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -9376,10 +9388,10 @@
         <v>688</v>
       </c>
       <c r="B288" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D288" t="s">
         <v>8</v>
@@ -9390,10 +9402,10 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" t="s">
+        <v>689</v>
+      </c>
+      <c r="B289" t="s">
         <v>690</v>
-      </c>
-      <c r="B289" t="s">
-        <v>686</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>691</v>
@@ -9410,7 +9422,7 @@
         <v>692</v>
       </c>
       <c r="B290" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>693</v>
@@ -9419,7 +9431,7 @@
         <v>8</v>
       </c>
       <c r="E290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -9427,27 +9439,27 @@
         <v>694</v>
       </c>
       <c r="B291" t="s">
+        <v>690</v>
+      </c>
+      <c r="C291" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="C291" s="1" t="s">
-        <v>696</v>
-      </c>
       <c r="D291" t="s">
         <v>8</v>
       </c>
       <c r="E291" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:5">
       <c r="A292" t="s">
+        <v>696</v>
+      </c>
+      <c r="B292" t="s">
+        <v>690</v>
+      </c>
+      <c r="C292" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="B292" t="s">
-        <v>698</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>699</v>
       </c>
       <c r="D292" t="s">
         <v>8</v>
@@ -9458,13 +9470,13 @@
     </row>
     <row r="293" spans="1:5">
       <c r="A293" t="s">
+        <v>698</v>
+      </c>
+      <c r="B293" t="s">
+        <v>699</v>
+      </c>
+      <c r="C293" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="B293" t="s">
-        <v>701</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>702</v>
       </c>
       <c r="D293" t="s">
         <v>8</v>
@@ -9475,13 +9487,13 @@
     </row>
     <row r="294" spans="1:5">
       <c r="A294" t="s">
+        <v>701</v>
+      </c>
+      <c r="B294" t="s">
+        <v>702</v>
+      </c>
+      <c r="C294" s="1" t="s">
         <v>703</v>
-      </c>
-      <c r="B294" t="s">
-        <v>704</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>705</v>
       </c>
       <c r="D294" t="s">
         <v>8</v>
@@ -9492,13 +9504,13 @@
     </row>
     <row r="295" spans="1:5">
       <c r="A295" t="s">
+        <v>704</v>
+      </c>
+      <c r="B295" t="s">
+        <v>705</v>
+      </c>
+      <c r="C295" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="B295" t="s">
-        <v>707</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="D295" t="s">
         <v>8</v>
@@ -9509,13 +9521,13 @@
     </row>
     <row r="296" spans="1:5">
       <c r="A296" t="s">
+        <v>707</v>
+      </c>
+      <c r="B296" t="s">
+        <v>708</v>
+      </c>
+      <c r="C296" s="1" t="s">
         <v>709</v>
-      </c>
-      <c r="B296" t="s">
-        <v>707</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>710</v>
       </c>
       <c r="D296" t="s">
         <v>8</v>
@@ -9526,30 +9538,30 @@
     </row>
     <row r="297" spans="1:5">
       <c r="A297" t="s">
+        <v>710</v>
+      </c>
+      <c r="B297" t="s">
         <v>711</v>
       </c>
-      <c r="B297" t="s">
+      <c r="C297" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="C297" s="1" t="s">
-        <v>713</v>
-      </c>
       <c r="D297" t="s">
         <v>8</v>
       </c>
       <c r="E297" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:5">
       <c r="A298" t="s">
+        <v>713</v>
+      </c>
+      <c r="B298" t="s">
+        <v>711</v>
+      </c>
+      <c r="C298" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="B298" t="s">
-        <v>715</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>716</v>
       </c>
       <c r="D298" t="s">
         <v>8</v>
@@ -9560,30 +9572,30 @@
     </row>
     <row r="299" spans="1:5">
       <c r="A299" t="s">
+        <v>715</v>
+      </c>
+      <c r="B299" t="s">
+        <v>716</v>
+      </c>
+      <c r="C299" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B299" t="s">
-        <v>718</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="D299" t="s">
         <v>8</v>
       </c>
       <c r="E299" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:5">
       <c r="A300" t="s">
+        <v>718</v>
+      </c>
+      <c r="B300" t="s">
+        <v>719</v>
+      </c>
+      <c r="C300" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="B300" t="s">
-        <v>718</v>
-      </c>
-      <c r="C300" s="1" t="s">
-        <v>721</v>
       </c>
       <c r="D300" t="s">
         <v>8</v>
@@ -9594,13 +9606,13 @@
     </row>
     <row r="301" spans="1:5">
       <c r="A301" t="s">
+        <v>721</v>
+      </c>
+      <c r="B301" t="s">
         <v>722</v>
       </c>
-      <c r="B301" t="s">
+      <c r="C301" s="1" t="s">
         <v>723</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>724</v>
       </c>
       <c r="D301" t="s">
         <v>8</v>
@@ -9611,13 +9623,13 @@
     </row>
     <row r="302" spans="1:5">
       <c r="A302" t="s">
+        <v>724</v>
+      </c>
+      <c r="B302" t="s">
+        <v>722</v>
+      </c>
+      <c r="C302" s="1" t="s">
         <v>725</v>
-      </c>
-      <c r="B302" t="s">
-        <v>726</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>727</v>
       </c>
       <c r="D302" t="s">
         <v>8</v>
@@ -9628,13 +9640,13 @@
     </row>
     <row r="303" spans="1:5">
       <c r="A303" t="s">
+        <v>726</v>
+      </c>
+      <c r="B303" t="s">
+        <v>727</v>
+      </c>
+      <c r="C303" s="1" t="s">
         <v>728</v>
-      </c>
-      <c r="B303" t="s">
-        <v>726</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>729</v>
       </c>
       <c r="D303" t="s">
         <v>8</v>
@@ -9645,10 +9657,10 @@
     </row>
     <row r="304" spans="1:5">
       <c r="A304" t="s">
+        <v>729</v>
+      </c>
+      <c r="B304" t="s">
         <v>730</v>
-      </c>
-      <c r="B304" t="s">
-        <v>726</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>731</v>
@@ -9665,27 +9677,27 @@
         <v>732</v>
       </c>
       <c r="B305" t="s">
+        <v>730</v>
+      </c>
+      <c r="C305" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="C305" s="1" t="s">
-        <v>734</v>
-      </c>
       <c r="D305" t="s">
         <v>8</v>
       </c>
       <c r="E305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:5">
       <c r="A306" t="s">
+        <v>734</v>
+      </c>
+      <c r="B306" t="s">
+        <v>730</v>
+      </c>
+      <c r="C306" s="1" t="s">
         <v>735</v>
-      </c>
-      <c r="B306" t="s">
-        <v>736</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>737</v>
       </c>
       <c r="D306" t="s">
         <v>8</v>
@@ -9696,13 +9708,13 @@
     </row>
     <row r="307" spans="1:5">
       <c r="A307" t="s">
+        <v>736</v>
+      </c>
+      <c r="B307" t="s">
+        <v>737</v>
+      </c>
+      <c r="C307" s="1" t="s">
         <v>738</v>
-      </c>
-      <c r="B307" t="s">
-        <v>739</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>740</v>
       </c>
       <c r="D307" t="s">
         <v>8</v>
@@ -9713,27 +9725,27 @@
     </row>
     <row r="308" spans="1:5">
       <c r="A308" t="s">
+        <v>739</v>
+      </c>
+      <c r="B308" t="s">
+        <v>740</v>
+      </c>
+      <c r="C308" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B308" t="s">
-        <v>739</v>
-      </c>
-      <c r="C308" s="1" t="s">
-        <v>742</v>
-      </c>
       <c r="D308" t="s">
         <v>8</v>
       </c>
       <c r="E308" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309" spans="1:5">
       <c r="A309" t="s">
+        <v>742</v>
+      </c>
+      <c r="B309" t="s">
         <v>743</v>
-      </c>
-      <c r="B309" t="s">
-        <v>739</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>744</v>
@@ -9742,7 +9754,7 @@
         <v>8</v>
       </c>
       <c r="E309" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -9750,10 +9762,10 @@
         <v>745</v>
       </c>
       <c r="B310" t="s">
+        <v>743</v>
+      </c>
+      <c r="C310" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="C310" s="1" t="s">
-        <v>747</v>
       </c>
       <c r="D310" t="s">
         <v>8</v>
@@ -9764,30 +9776,30 @@
     </row>
     <row r="311" spans="1:5">
       <c r="A311" t="s">
+        <v>747</v>
+      </c>
+      <c r="B311" t="s">
+        <v>743</v>
+      </c>
+      <c r="C311" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="B311" t="s">
-        <v>746</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>749</v>
-      </c>
       <c r="D311" t="s">
         <v>8</v>
       </c>
       <c r="E311" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:5">
       <c r="A312" t="s">
+        <v>749</v>
+      </c>
+      <c r="B312" t="s">
         <v>750</v>
       </c>
-      <c r="B312" t="s">
+      <c r="C312" s="1" t="s">
         <v>751</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>752</v>
       </c>
       <c r="D312" t="s">
         <v>8</v>
@@ -9798,13 +9810,13 @@
     </row>
     <row r="313" spans="1:5">
       <c r="A313" t="s">
+        <v>752</v>
+      </c>
+      <c r="B313" t="s">
+        <v>750</v>
+      </c>
+      <c r="C313" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="B313" t="s">
-        <v>751</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>754</v>
       </c>
       <c r="D313" t="s">
         <v>8</v>
@@ -9815,19 +9827,19 @@
     </row>
     <row r="314" spans="1:5">
       <c r="A314" t="s">
+        <v>754</v>
+      </c>
+      <c r="B314" t="s">
         <v>755</v>
-      </c>
-      <c r="B314" t="s">
-        <v>751</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>756</v>
       </c>
       <c r="D314" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -9835,7 +9847,10 @@
         <v>757</v>
       </c>
       <c r="B315" t="s">
-        <v>751</v>
+        <v>755</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>758</v>
       </c>
       <c r="D315" t="s">
         <v>8</v>
@@ -9846,16 +9861,16 @@
     </row>
     <row r="316" spans="1:5">
       <c r="A316" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B316" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>760</v>
       </c>
       <c r="D316" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E316" t="b">
         <v>0</v>
@@ -9866,24 +9881,21 @@
         <v>761</v>
       </c>
       <c r="B317" t="s">
-        <v>759</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="D317" t="s">
         <v>8</v>
       </c>
       <c r="E317" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:5">
       <c r="A318" t="s">
+        <v>762</v>
+      </c>
+      <c r="B318" t="s">
         <v>763</v>
-      </c>
-      <c r="B318" t="s">
-        <v>759</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>764</v>
@@ -9892,7 +9904,7 @@
         <v>8</v>
       </c>
       <c r="E318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -9900,27 +9912,27 @@
         <v>765</v>
       </c>
       <c r="B319" t="s">
+        <v>763</v>
+      </c>
+      <c r="C319" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="C319" s="1" t="s">
-        <v>767</v>
-      </c>
       <c r="D319" t="s">
         <v>8</v>
       </c>
       <c r="E319" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:5">
       <c r="A320" t="s">
+        <v>767</v>
+      </c>
+      <c r="B320" t="s">
+        <v>763</v>
+      </c>
+      <c r="C320" s="1" t="s">
         <v>768</v>
-      </c>
-      <c r="B320" t="s">
-        <v>766</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>769</v>
       </c>
       <c r="D320" t="s">
         <v>8</v>
@@ -9931,13 +9943,13 @@
     </row>
     <row r="321" spans="1:5">
       <c r="A321" t="s">
+        <v>769</v>
+      </c>
+      <c r="B321" t="s">
         <v>770</v>
       </c>
-      <c r="B321" t="s">
+      <c r="C321" s="1" t="s">
         <v>771</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>772</v>
       </c>
       <c r="D321" t="s">
         <v>8</v>
@@ -9948,13 +9960,13 @@
     </row>
     <row r="322" spans="1:5">
       <c r="A322" t="s">
+        <v>772</v>
+      </c>
+      <c r="B322" t="s">
+        <v>770</v>
+      </c>
+      <c r="C322" s="1" t="s">
         <v>773</v>
-      </c>
-      <c r="B322" t="s">
-        <v>771</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>774</v>
       </c>
       <c r="D322" t="s">
         <v>8</v>
@@ -9965,13 +9977,13 @@
     </row>
     <row r="323" spans="1:5">
       <c r="A323" t="s">
+        <v>774</v>
+      </c>
+      <c r="B323" t="s">
         <v>775</v>
       </c>
-      <c r="B323" t="s">
+      <c r="C323" s="1" t="s">
         <v>776</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>777</v>
       </c>
       <c r="D323" t="s">
         <v>8</v>
@@ -9982,13 +9994,13 @@
     </row>
     <row r="324" spans="1:5">
       <c r="A324" t="s">
+        <v>777</v>
+      </c>
+      <c r="B324" t="s">
+        <v>775</v>
+      </c>
+      <c r="C324" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="B324" t="s">
-        <v>779</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>780</v>
       </c>
       <c r="D324" t="s">
         <v>8</v>
@@ -9999,13 +10011,13 @@
     </row>
     <row r="325" spans="1:5">
       <c r="A325" t="s">
+        <v>779</v>
+      </c>
+      <c r="B325" t="s">
+        <v>780</v>
+      </c>
+      <c r="C325" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="B325" t="s">
-        <v>782</v>
-      </c>
-      <c r="C325" s="1" t="s">
-        <v>783</v>
       </c>
       <c r="D325" t="s">
         <v>8</v>
@@ -10016,13 +10028,13 @@
     </row>
     <row r="326" spans="1:5">
       <c r="A326" t="s">
+        <v>782</v>
+      </c>
+      <c r="B326" t="s">
+        <v>783</v>
+      </c>
+      <c r="C326" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="B326" t="s">
-        <v>782</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>785</v>
       </c>
       <c r="D326" t="s">
         <v>8</v>
@@ -10033,13 +10045,13 @@
     </row>
     <row r="327" spans="1:5">
       <c r="A327" t="s">
+        <v>785</v>
+      </c>
+      <c r="B327" t="s">
         <v>786</v>
       </c>
-      <c r="B327" t="s">
+      <c r="C327" s="1" t="s">
         <v>787</v>
-      </c>
-      <c r="C327" s="1" t="s">
-        <v>788</v>
       </c>
       <c r="D327" t="s">
         <v>8</v>
@@ -10050,13 +10062,13 @@
     </row>
     <row r="328" spans="1:5">
       <c r="A328" t="s">
+        <v>788</v>
+      </c>
+      <c r="B328" t="s">
+        <v>786</v>
+      </c>
+      <c r="C328" s="1" t="s">
         <v>789</v>
-      </c>
-      <c r="B328" t="s">
-        <v>787</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>790</v>
       </c>
       <c r="D328" t="s">
         <v>8</v>
@@ -10067,13 +10079,13 @@
     </row>
     <row r="329" spans="1:5">
       <c r="A329" t="s">
+        <v>790</v>
+      </c>
+      <c r="B329" t="s">
         <v>791</v>
       </c>
-      <c r="B329" t="s">
+      <c r="C329" s="1" t="s">
         <v>792</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>793</v>
       </c>
       <c r="D329" t="s">
         <v>8</v>
@@ -10084,30 +10096,30 @@
     </row>
     <row r="330" spans="1:5">
       <c r="A330" t="s">
+        <v>793</v>
+      </c>
+      <c r="B330" t="s">
+        <v>791</v>
+      </c>
+      <c r="C330" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="B330" t="s">
-        <v>792</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>795</v>
-      </c>
       <c r="D330" t="s">
         <v>8</v>
       </c>
       <c r="E330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:5">
       <c r="A331" t="s">
+        <v>795</v>
+      </c>
+      <c r="B331" t="s">
         <v>796</v>
       </c>
-      <c r="B331" t="s">
+      <c r="C331" s="1" t="s">
         <v>797</v>
-      </c>
-      <c r="C331" s="1" t="s">
-        <v>798</v>
       </c>
       <c r="D331" t="s">
         <v>8</v>
@@ -10118,30 +10130,30 @@
     </row>
     <row r="332" spans="1:5">
       <c r="A332" t="s">
+        <v>798</v>
+      </c>
+      <c r="B332" t="s">
+        <v>796</v>
+      </c>
+      <c r="C332" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B332" t="s">
-        <v>800</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>801</v>
-      </c>
       <c r="D332" t="s">
         <v>8</v>
       </c>
       <c r="E332" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:5">
       <c r="A333" t="s">
+        <v>800</v>
+      </c>
+      <c r="B333" t="s">
+        <v>801</v>
+      </c>
+      <c r="C333" s="1" t="s">
         <v>802</v>
-      </c>
-      <c r="B333" t="s">
-        <v>800</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>803</v>
       </c>
       <c r="D333" t="s">
         <v>8</v>
@@ -10152,30 +10164,30 @@
     </row>
     <row r="334" spans="1:5">
       <c r="A334" t="s">
+        <v>803</v>
+      </c>
+      <c r="B334" t="s">
         <v>804</v>
       </c>
-      <c r="B334" t="s">
+      <c r="C334" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="C334" s="1" t="s">
-        <v>806</v>
-      </c>
       <c r="D334" t="s">
         <v>8</v>
       </c>
       <c r="E334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:5">
       <c r="A335" t="s">
+        <v>806</v>
+      </c>
+      <c r="B335" t="s">
+        <v>804</v>
+      </c>
+      <c r="C335" s="1" t="s">
         <v>807</v>
-      </c>
-      <c r="B335" t="s">
-        <v>808</v>
-      </c>
-      <c r="C335" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="D335" t="s">
         <v>8</v>
@@ -10186,13 +10198,13 @@
     </row>
     <row r="336" spans="1:5">
       <c r="A336" t="s">
+        <v>808</v>
+      </c>
+      <c r="B336" t="s">
+        <v>809</v>
+      </c>
+      <c r="C336" s="1" t="s">
         <v>810</v>
-      </c>
-      <c r="B336" t="s">
-        <v>811</v>
-      </c>
-      <c r="C336" s="1" t="s">
-        <v>812</v>
       </c>
       <c r="D336" t="s">
         <v>8</v>
@@ -10203,27 +10215,27 @@
     </row>
     <row r="337" spans="1:5">
       <c r="A337" t="s">
+        <v>811</v>
+      </c>
+      <c r="B337" t="s">
+        <v>812</v>
+      </c>
+      <c r="C337" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="B337" t="s">
-        <v>811</v>
-      </c>
-      <c r="C337" s="1" t="s">
-        <v>814</v>
-      </c>
       <c r="D337" t="s">
         <v>8</v>
       </c>
       <c r="E337" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:5">
       <c r="A338" t="s">
+        <v>814</v>
+      </c>
+      <c r="B338" t="s">
         <v>815</v>
-      </c>
-      <c r="B338" t="s">
-        <v>811</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>816</v>
@@ -10240,7 +10252,7 @@
         <v>817</v>
       </c>
       <c r="B339" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>818</v>
@@ -10249,7 +10261,7 @@
         <v>8</v>
       </c>
       <c r="E339" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -10257,24 +10269,27 @@
         <v>819</v>
       </c>
       <c r="B340" t="s">
+        <v>815</v>
+      </c>
+      <c r="C340" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="C340" s="1" t="s">
-        <v>821</v>
-      </c>
       <c r="D340" t="s">
         <v>8</v>
       </c>
       <c r="E340" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:5">
       <c r="A341" t="s">
+        <v>821</v>
+      </c>
+      <c r="B341" t="s">
+        <v>815</v>
+      </c>
+      <c r="C341" s="1" t="s">
         <v>822</v>
-      </c>
-      <c r="B341" t="s">
-        <v>820</v>
       </c>
       <c r="D341" t="s">
         <v>8</v>
@@ -10297,7 +10312,7 @@
         <v>8</v>
       </c>
       <c r="E342" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -10305,10 +10320,7 @@
         <v>826</v>
       </c>
       <c r="B343" t="s">
-        <v>827</v>
-      </c>
-      <c r="C343" s="1" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="D343" t="s">
         <v>8</v>
@@ -10319,13 +10331,13 @@
     </row>
     <row r="344" spans="1:5">
       <c r="A344" t="s">
+        <v>827</v>
+      </c>
+      <c r="B344" t="s">
+        <v>828</v>
+      </c>
+      <c r="C344" s="1" t="s">
         <v>829</v>
-      </c>
-      <c r="B344" t="s">
-        <v>830</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>831</v>
       </c>
       <c r="D344" t="s">
         <v>8</v>
@@ -10336,13 +10348,13 @@
     </row>
     <row r="345" spans="1:5">
       <c r="A345" t="s">
+        <v>830</v>
+      </c>
+      <c r="B345" t="s">
+        <v>831</v>
+      </c>
+      <c r="C345" s="1" t="s">
         <v>832</v>
-      </c>
-      <c r="B345" t="s">
-        <v>833</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>834</v>
       </c>
       <c r="D345" t="s">
         <v>8</v>
@@ -10353,30 +10365,30 @@
     </row>
     <row r="346" spans="1:5">
       <c r="A346" t="s">
+        <v>833</v>
+      </c>
+      <c r="B346" t="s">
+        <v>834</v>
+      </c>
+      <c r="C346" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="B346" t="s">
-        <v>836</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>837</v>
-      </c>
       <c r="D346" t="s">
         <v>8</v>
       </c>
       <c r="E346" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:5">
       <c r="A347" t="s">
+        <v>836</v>
+      </c>
+      <c r="B347" t="s">
+        <v>837</v>
+      </c>
+      <c r="C347" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="B347" t="s">
-        <v>839</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>840</v>
       </c>
       <c r="D347" t="s">
         <v>8</v>
@@ -10387,30 +10399,30 @@
     </row>
     <row r="348" spans="1:5">
       <c r="A348" t="s">
+        <v>839</v>
+      </c>
+      <c r="B348" t="s">
+        <v>840</v>
+      </c>
+      <c r="C348" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="B348" t="s">
-        <v>842</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>843</v>
-      </c>
       <c r="D348" t="s">
         <v>8</v>
       </c>
       <c r="E348" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349" spans="1:5">
       <c r="A349" t="s">
+        <v>842</v>
+      </c>
+      <c r="B349" t="s">
+        <v>843</v>
+      </c>
+      <c r="C349" s="1" t="s">
         <v>844</v>
-      </c>
-      <c r="B349" t="s">
-        <v>845</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>846</v>
       </c>
       <c r="D349" t="s">
         <v>8</v>
@@ -10421,30 +10433,30 @@
     </row>
     <row r="350" spans="1:5">
       <c r="A350" t="s">
+        <v>845</v>
+      </c>
+      <c r="B350" t="s">
+        <v>846</v>
+      </c>
+      <c r="C350" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="B350" t="s">
-        <v>845</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>848</v>
-      </c>
       <c r="D350" t="s">
         <v>8</v>
       </c>
       <c r="E350" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:5">
       <c r="A351" t="s">
+        <v>848</v>
+      </c>
+      <c r="B351" t="s">
         <v>849</v>
       </c>
-      <c r="B351" t="s">
+      <c r="C351" s="1" t="s">
         <v>850</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>851</v>
       </c>
       <c r="D351" t="s">
         <v>8</v>
@@ -10455,44 +10467,44 @@
     </row>
     <row r="352" spans="1:5">
       <c r="A352" t="s">
+        <v>851</v>
+      </c>
+      <c r="B352" t="s">
+        <v>849</v>
+      </c>
+      <c r="C352" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="B352" t="s">
-        <v>853</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>854</v>
-      </c>
       <c r="D352" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E352" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353" spans="1:5">
       <c r="A353" t="s">
+        <v>853</v>
+      </c>
+      <c r="B353" t="s">
+        <v>854</v>
+      </c>
+      <c r="C353" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="B353" t="s">
-        <v>853</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>856</v>
-      </c>
       <c r="D353" t="s">
         <v>8</v>
       </c>
       <c r="E353" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:5">
       <c r="A354" t="s">
+        <v>856</v>
+      </c>
+      <c r="B354" t="s">
         <v>857</v>
-      </c>
-      <c r="B354" t="s">
-        <v>853</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>858</v>
@@ -10509,7 +10521,7 @@
         <v>859</v>
       </c>
       <c r="B355" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>860</v>
@@ -10518,7 +10530,7 @@
         <v>8</v>
       </c>
       <c r="E355" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -10526,13 +10538,13 @@
         <v>861</v>
       </c>
       <c r="B356" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>862</v>
       </c>
       <c r="D356" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E356" t="b">
         <v>0</v>
@@ -10543,27 +10555,27 @@
         <v>863</v>
       </c>
       <c r="B357" t="s">
+        <v>857</v>
+      </c>
+      <c r="C357" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="C357" s="1" t="s">
-        <v>865</v>
-      </c>
       <c r="D357" t="s">
         <v>8</v>
       </c>
       <c r="E357" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:5">
       <c r="A358" t="s">
+        <v>865</v>
+      </c>
+      <c r="B358" t="s">
+        <v>857</v>
+      </c>
+      <c r="C358" s="1" t="s">
         <v>866</v>
-      </c>
-      <c r="B358" t="s">
-        <v>864</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>867</v>
       </c>
       <c r="D358" t="s">
         <v>8</v>
@@ -10574,10 +10586,10 @@
     </row>
     <row r="359" spans="1:5">
       <c r="A359" t="s">
+        <v>867</v>
+      </c>
+      <c r="B359" t="s">
         <v>868</v>
-      </c>
-      <c r="B359" t="s">
-        <v>864</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>869</v>
@@ -10594,7 +10606,7 @@
         <v>870</v>
       </c>
       <c r="B360" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>871</v>
@@ -10611,75 +10623,75 @@
         <v>872</v>
       </c>
       <c r="B361" t="s">
+        <v>868</v>
+      </c>
+      <c r="C361" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="C361" s="1" t="s">
-        <v>874</v>
-      </c>
       <c r="D361" t="s">
         <v>8</v>
       </c>
       <c r="E361" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362" spans="1:5">
       <c r="A362" t="s">
+        <v>874</v>
+      </c>
+      <c r="B362" t="s">
+        <v>868</v>
+      </c>
+      <c r="C362" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="B362" t="s">
-        <v>873</v>
-      </c>
-      <c r="C362" s="1" t="s">
-        <v>876</v>
-      </c>
       <c r="D362" t="s">
         <v>8</v>
       </c>
       <c r="E362" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:5">
       <c r="A363" t="s">
+        <v>876</v>
+      </c>
+      <c r="B363" t="s">
         <v>877</v>
       </c>
-      <c r="B363" t="s">
+      <c r="C363" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="C363" s="1" t="s">
-        <v>879</v>
-      </c>
       <c r="D363" t="s">
         <v>8</v>
       </c>
       <c r="E363" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:5">
       <c r="A364" t="s">
+        <v>879</v>
+      </c>
+      <c r="B364" t="s">
+        <v>877</v>
+      </c>
+      <c r="C364" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B364" t="s">
-        <v>878</v>
-      </c>
-      <c r="C364" s="1" t="s">
-        <v>881</v>
-      </c>
       <c r="D364" t="s">
         <v>8</v>
       </c>
       <c r="E364" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" spans="1:5">
       <c r="A365" t="s">
+        <v>881</v>
+      </c>
+      <c r="B365" t="s">
         <v>882</v>
-      </c>
-      <c r="B365" t="s">
-        <v>878</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>883</v>
@@ -10688,7 +10700,7 @@
         <v>8</v>
       </c>
       <c r="E365" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -10696,7 +10708,7 @@
         <v>884</v>
       </c>
       <c r="B366" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>885</v>
@@ -10713,41 +10725,41 @@
         <v>886</v>
       </c>
       <c r="B367" t="s">
+        <v>882</v>
+      </c>
+      <c r="C367" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="C367" s="1" t="s">
-        <v>888</v>
-      </c>
       <c r="D367" t="s">
         <v>8</v>
       </c>
       <c r="E367" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:5">
       <c r="A368" t="s">
+        <v>888</v>
+      </c>
+      <c r="B368" t="s">
+        <v>882</v>
+      </c>
+      <c r="C368" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="B368" t="s">
-        <v>887</v>
-      </c>
-      <c r="C368" s="1" t="s">
-        <v>890</v>
-      </c>
       <c r="D368" t="s">
         <v>8</v>
       </c>
       <c r="E368" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:5">
       <c r="A369" t="s">
+        <v>890</v>
+      </c>
+      <c r="B369" t="s">
         <v>891</v>
-      </c>
-      <c r="B369" t="s">
-        <v>887</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>892</v>
@@ -10756,7 +10768,7 @@
         <v>8</v>
       </c>
       <c r="E369" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -10764,44 +10776,44 @@
         <v>893</v>
       </c>
       <c r="B370" t="s">
+        <v>891</v>
+      </c>
+      <c r="C370" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="C370" s="1" t="s">
-        <v>895</v>
-      </c>
       <c r="D370" t="s">
         <v>8</v>
       </c>
       <c r="E370" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371" spans="1:5">
       <c r="A371" t="s">
+        <v>895</v>
+      </c>
+      <c r="B371" t="s">
+        <v>891</v>
+      </c>
+      <c r="C371" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="B371" t="s">
-        <v>897</v>
-      </c>
-      <c r="C371" s="1" t="s">
-        <v>898</v>
-      </c>
       <c r="D371" t="s">
         <v>8</v>
       </c>
       <c r="E371" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:5">
       <c r="A372" t="s">
+        <v>897</v>
+      </c>
+      <c r="B372" t="s">
+        <v>898</v>
+      </c>
+      <c r="C372" s="1" t="s">
         <v>899</v>
-      </c>
-      <c r="B372" t="s">
-        <v>897</v>
-      </c>
-      <c r="C372" s="1" t="s">
-        <v>900</v>
       </c>
       <c r="D372" t="s">
         <v>8</v>
@@ -10812,47 +10824,47 @@
     </row>
     <row r="373" spans="1:5">
       <c r="A373" t="s">
+        <v>900</v>
+      </c>
+      <c r="B373" t="s">
         <v>901</v>
       </c>
-      <c r="B373" t="s">
+      <c r="C373" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="C373" s="1" t="s">
-        <v>903</v>
-      </c>
       <c r="D373" t="s">
         <v>8</v>
       </c>
       <c r="E373" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374" spans="1:5">
       <c r="A374" t="s">
+        <v>903</v>
+      </c>
+      <c r="B374" t="s">
+        <v>901</v>
+      </c>
+      <c r="C374" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="B374" t="s">
-        <v>905</v>
-      </c>
-      <c r="C374" s="1" t="s">
-        <v>906</v>
-      </c>
       <c r="D374" t="s">
         <v>8</v>
       </c>
       <c r="E374" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:5">
       <c r="A375" t="s">
+        <v>905</v>
+      </c>
+      <c r="B375" t="s">
+        <v>906</v>
+      </c>
+      <c r="C375" s="1" t="s">
         <v>907</v>
-      </c>
-      <c r="B375" t="s">
-        <v>905</v>
-      </c>
-      <c r="C375" s="1" t="s">
-        <v>908</v>
       </c>
       <c r="D375" t="s">
         <v>8</v>
@@ -10863,10 +10875,10 @@
     </row>
     <row r="376" spans="1:5">
       <c r="A376" t="s">
+        <v>908</v>
+      </c>
+      <c r="B376" t="s">
         <v>909</v>
-      </c>
-      <c r="B376" t="s">
-        <v>905</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>910</v>
@@ -10883,7 +10895,7 @@
         <v>911</v>
       </c>
       <c r="B377" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>912</v>
@@ -10892,7 +10904,7 @@
         <v>8</v>
       </c>
       <c r="E377" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -10900,10 +10912,10 @@
         <v>913</v>
       </c>
       <c r="B378" t="s">
+        <v>909</v>
+      </c>
+      <c r="C378" s="1" t="s">
         <v>914</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>915</v>
       </c>
       <c r="D378" t="s">
         <v>8</v>
@@ -10914,30 +10926,30 @@
     </row>
     <row r="379" spans="1:5">
       <c r="A379" t="s">
+        <v>915</v>
+      </c>
+      <c r="B379" t="s">
+        <v>909</v>
+      </c>
+      <c r="C379" s="1" t="s">
         <v>916</v>
       </c>
-      <c r="B379" t="s">
-        <v>917</v>
-      </c>
-      <c r="C379" s="1" t="s">
-        <v>918</v>
-      </c>
       <c r="D379" t="s">
         <v>8</v>
       </c>
       <c r="E379" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380" spans="1:5">
       <c r="A380" t="s">
+        <v>917</v>
+      </c>
+      <c r="B380" t="s">
+        <v>918</v>
+      </c>
+      <c r="C380" s="1" t="s">
         <v>919</v>
-      </c>
-      <c r="B380" t="s">
-        <v>917</v>
-      </c>
-      <c r="C380" s="1" t="s">
-        <v>920</v>
       </c>
       <c r="D380" t="s">
         <v>8</v>
@@ -10948,10 +10960,10 @@
     </row>
     <row r="381" spans="1:5">
       <c r="A381" t="s">
+        <v>920</v>
+      </c>
+      <c r="B381" t="s">
         <v>921</v>
-      </c>
-      <c r="B381" t="s">
-        <v>917</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>922</v>
@@ -10968,27 +10980,27 @@
         <v>923</v>
       </c>
       <c r="B382" t="s">
+        <v>921</v>
+      </c>
+      <c r="C382" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="C382" s="1" t="s">
-        <v>925</v>
-      </c>
       <c r="D382" t="s">
         <v>8</v>
       </c>
       <c r="E382" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383" spans="1:5">
       <c r="A383" t="s">
+        <v>925</v>
+      </c>
+      <c r="B383" t="s">
+        <v>921</v>
+      </c>
+      <c r="C383" s="1" t="s">
         <v>926</v>
-      </c>
-      <c r="B383" t="s">
-        <v>924</v>
-      </c>
-      <c r="C383" s="1" t="s">
-        <v>927</v>
       </c>
       <c r="D383" t="s">
         <v>8</v>
@@ -10999,44 +11011,44 @@
     </row>
     <row r="384" spans="1:5">
       <c r="A384" t="s">
+        <v>927</v>
+      </c>
+      <c r="B384" t="s">
         <v>928</v>
       </c>
-      <c r="B384" t="s">
+      <c r="C384" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="C384" s="1" t="s">
-        <v>930</v>
-      </c>
       <c r="D384" t="s">
         <v>8</v>
       </c>
       <c r="E384" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385" spans="1:5">
       <c r="A385" t="s">
+        <v>930</v>
+      </c>
+      <c r="B385" t="s">
+        <v>928</v>
+      </c>
+      <c r="C385" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="B385" t="s">
-        <v>929</v>
-      </c>
-      <c r="C385" s="1" t="s">
-        <v>932</v>
-      </c>
       <c r="D385" t="s">
         <v>8</v>
       </c>
       <c r="E385" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386" spans="1:5">
       <c r="A386" t="s">
+        <v>932</v>
+      </c>
+      <c r="B386" t="s">
         <v>933</v>
-      </c>
-      <c r="B386" t="s">
-        <v>929</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>934</v>
@@ -11053,7 +11065,7 @@
         <v>935</v>
       </c>
       <c r="B387" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>936</v>
@@ -11062,7 +11074,7 @@
         <v>8</v>
       </c>
       <c r="E387" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -11070,10 +11082,10 @@
         <v>937</v>
       </c>
       <c r="B388" t="s">
+        <v>933</v>
+      </c>
+      <c r="C388" s="1" t="s">
         <v>938</v>
-      </c>
-      <c r="C388" s="1" t="s">
-        <v>939</v>
       </c>
       <c r="D388" t="s">
         <v>8</v>
@@ -11084,13 +11096,13 @@
     </row>
     <row r="389" spans="1:5">
       <c r="A389" t="s">
+        <v>939</v>
+      </c>
+      <c r="B389" t="s">
+        <v>933</v>
+      </c>
+      <c r="C389" s="1" t="s">
         <v>940</v>
-      </c>
-      <c r="B389" t="s">
-        <v>941</v>
-      </c>
-      <c r="C389" s="1" t="s">
-        <v>942</v>
       </c>
       <c r="D389" t="s">
         <v>8</v>
@@ -11101,44 +11113,44 @@
     </row>
     <row r="390" spans="1:5">
       <c r="A390" t="s">
+        <v>941</v>
+      </c>
+      <c r="B390" t="s">
+        <v>942</v>
+      </c>
+      <c r="C390" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="B390" t="s">
-        <v>944</v>
-      </c>
-      <c r="C390" s="1" t="s">
-        <v>945</v>
-      </c>
       <c r="D390" t="s">
         <v>8</v>
       </c>
       <c r="E390" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" spans="1:5">
       <c r="A391" t="s">
+        <v>944</v>
+      </c>
+      <c r="B391" t="s">
+        <v>945</v>
+      </c>
+      <c r="C391" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="B391" t="s">
-        <v>944</v>
-      </c>
-      <c r="C391" s="1" t="s">
-        <v>947</v>
-      </c>
       <c r="D391" t="s">
         <v>8</v>
       </c>
       <c r="E391" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392" spans="1:5">
       <c r="A392" t="s">
+        <v>947</v>
+      </c>
+      <c r="B392" t="s">
         <v>948</v>
-      </c>
-      <c r="B392" t="s">
-        <v>944</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>949</v>
@@ -11147,7 +11159,7 @@
         <v>8</v>
       </c>
       <c r="E392" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -11155,61 +11167,61 @@
         <v>950</v>
       </c>
       <c r="B393" t="s">
+        <v>948</v>
+      </c>
+      <c r="C393" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C393" s="1" t="s">
-        <v>952</v>
-      </c>
       <c r="D393" t="s">
         <v>8</v>
       </c>
       <c r="E393" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394" spans="1:5">
       <c r="A394" t="s">
+        <v>952</v>
+      </c>
+      <c r="B394" t="s">
+        <v>948</v>
+      </c>
+      <c r="C394" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="B394" t="s">
-        <v>954</v>
-      </c>
-      <c r="C394" s="1" t="s">
-        <v>955</v>
-      </c>
       <c r="D394" t="s">
         <v>8</v>
       </c>
       <c r="E394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395" spans="1:5">
       <c r="A395" t="s">
+        <v>954</v>
+      </c>
+      <c r="B395" t="s">
+        <v>955</v>
+      </c>
+      <c r="C395" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="B395" t="s">
-        <v>954</v>
-      </c>
-      <c r="C395" s="1" t="s">
-        <v>957</v>
-      </c>
       <c r="D395" t="s">
         <v>8</v>
       </c>
       <c r="E395" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396" spans="1:5">
       <c r="A396" t="s">
+        <v>957</v>
+      </c>
+      <c r="B396" t="s">
         <v>958</v>
       </c>
-      <c r="B396" t="s">
+      <c r="C396" s="1" t="s">
         <v>959</v>
-      </c>
-      <c r="C396" s="1" t="s">
-        <v>960</v>
       </c>
       <c r="D396" t="s">
         <v>8</v>
@@ -11220,13 +11232,13 @@
     </row>
     <row r="397" spans="1:5">
       <c r="A397" t="s">
+        <v>960</v>
+      </c>
+      <c r="B397" t="s">
+        <v>958</v>
+      </c>
+      <c r="C397" s="1" t="s">
         <v>961</v>
-      </c>
-      <c r="B397" t="s">
-        <v>959</v>
-      </c>
-      <c r="C397" s="1" t="s">
-        <v>962</v>
       </c>
       <c r="D397" t="s">
         <v>8</v>
@@ -11237,10 +11249,10 @@
     </row>
     <row r="398" spans="1:5">
       <c r="A398" t="s">
+        <v>962</v>
+      </c>
+      <c r="B398" t="s">
         <v>963</v>
-      </c>
-      <c r="B398" t="s">
-        <v>959</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>964</v>
@@ -11249,7 +11261,7 @@
         <v>8</v>
       </c>
       <c r="E398" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -11257,27 +11269,27 @@
         <v>965</v>
       </c>
       <c r="B399" t="s">
+        <v>963</v>
+      </c>
+      <c r="C399" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="C399" s="1" t="s">
-        <v>967</v>
-      </c>
       <c r="D399" t="s">
         <v>8</v>
       </c>
       <c r="E399" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400" spans="1:5">
       <c r="A400" t="s">
+        <v>967</v>
+      </c>
+      <c r="B400" t="s">
+        <v>963</v>
+      </c>
+      <c r="C400" s="1" t="s">
         <v>968</v>
-      </c>
-      <c r="B400" t="s">
-        <v>969</v>
-      </c>
-      <c r="C400" s="1" t="s">
-        <v>970</v>
       </c>
       <c r="D400" t="s">
         <v>8</v>
@@ -11288,30 +11300,30 @@
     </row>
     <row r="401" spans="1:5">
       <c r="A401" t="s">
+        <v>969</v>
+      </c>
+      <c r="B401" t="s">
+        <v>970</v>
+      </c>
+      <c r="C401" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="B401" t="s">
-        <v>969</v>
-      </c>
-      <c r="C401" s="1" t="s">
-        <v>972</v>
-      </c>
       <c r="D401" t="s">
         <v>8</v>
       </c>
       <c r="E401" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402" spans="1:5">
       <c r="A402" t="s">
+        <v>972</v>
+      </c>
+      <c r="B402" t="s">
         <v>973</v>
       </c>
-      <c r="B402" t="s">
+      <c r="C402" s="1" t="s">
         <v>974</v>
-      </c>
-      <c r="C402" s="1" t="s">
-        <v>975</v>
       </c>
       <c r="D402" t="s">
         <v>8</v>
@@ -11322,13 +11334,13 @@
     </row>
     <row r="403" spans="1:5">
       <c r="A403" t="s">
+        <v>975</v>
+      </c>
+      <c r="B403" t="s">
+        <v>973</v>
+      </c>
+      <c r="C403" s="1" t="s">
         <v>976</v>
-      </c>
-      <c r="B403" t="s">
-        <v>974</v>
-      </c>
-      <c r="C403" s="1" t="s">
-        <v>977</v>
       </c>
       <c r="D403" t="s">
         <v>8</v>
@@ -11339,30 +11351,30 @@
     </row>
     <row r="404" spans="1:5">
       <c r="A404" t="s">
+        <v>977</v>
+      </c>
+      <c r="B404" t="s">
         <v>978</v>
       </c>
-      <c r="B404" t="s">
+      <c r="C404" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="C404" s="1" t="s">
-        <v>980</v>
-      </c>
       <c r="D404" t="s">
         <v>8</v>
       </c>
       <c r="E404" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405" spans="1:5">
       <c r="A405" t="s">
+        <v>980</v>
+      </c>
+      <c r="B405" t="s">
+        <v>978</v>
+      </c>
+      <c r="C405" s="1" t="s">
         <v>981</v>
-      </c>
-      <c r="B405" t="s">
-        <v>979</v>
-      </c>
-      <c r="C405" s="1" t="s">
-        <v>982</v>
       </c>
       <c r="D405" t="s">
         <v>8</v>
@@ -11373,16 +11385,16 @@
     </row>
     <row r="406" spans="1:5">
       <c r="A406" t="s">
+        <v>982</v>
+      </c>
+      <c r="B406" t="s">
         <v>983</v>
-      </c>
-      <c r="B406" t="s">
-        <v>979</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>984</v>
       </c>
       <c r="D406" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E406" t="b">
         <v>0</v>
@@ -11393,7 +11405,7 @@
         <v>985</v>
       </c>
       <c r="B407" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>986</v>
@@ -11410,13 +11422,13 @@
         <v>987</v>
       </c>
       <c r="B408" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>988</v>
       </c>
       <c r="D408" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E408" t="b">
         <v>0</v>
@@ -11427,7 +11439,7 @@
         <v>989</v>
       </c>
       <c r="B409" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>990</v>
@@ -11436,7 +11448,7 @@
         <v>8</v>
       </c>
       <c r="E409" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -11444,10 +11456,10 @@
         <v>991</v>
       </c>
       <c r="B410" t="s">
+        <v>983</v>
+      </c>
+      <c r="C410" s="1" t="s">
         <v>992</v>
-      </c>
-      <c r="C410" s="1" t="s">
-        <v>993</v>
       </c>
       <c r="D410" t="s">
         <v>8</v>
@@ -11458,27 +11470,27 @@
     </row>
     <row r="411" spans="1:5">
       <c r="A411" t="s">
+        <v>993</v>
+      </c>
+      <c r="B411" t="s">
+        <v>983</v>
+      </c>
+      <c r="C411" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="B411" t="s">
-        <v>992</v>
-      </c>
-      <c r="C411" s="1" t="s">
-        <v>995</v>
-      </c>
       <c r="D411" t="s">
         <v>8</v>
       </c>
       <c r="E411" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412" spans="1:5">
       <c r="A412" t="s">
+        <v>995</v>
+      </c>
+      <c r="B412" t="s">
         <v>996</v>
-      </c>
-      <c r="B412" t="s">
-        <v>992</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>997</v>
@@ -11487,7 +11499,7 @@
         <v>8</v>
       </c>
       <c r="E412" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -11495,7 +11507,7 @@
         <v>998</v>
       </c>
       <c r="B413" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>999</v>
@@ -11512,44 +11524,44 @@
         <v>1000</v>
       </c>
       <c r="B414" t="s">
+        <v>996</v>
+      </c>
+      <c r="C414" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="C414" s="1" t="s">
-        <v>1002</v>
-      </c>
       <c r="D414" t="s">
         <v>8</v>
       </c>
       <c r="E414" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415" spans="1:5">
       <c r="A415" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B415" t="s">
+        <v>996</v>
+      </c>
+      <c r="C415" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="B415" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C415" s="1" t="s">
-        <v>1005</v>
-      </c>
       <c r="D415" t="s">
         <v>8</v>
       </c>
       <c r="E415" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416" spans="1:5">
       <c r="A416" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C416" s="1" t="s">
         <v>1006</v>
-      </c>
-      <c r="B416" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C416" s="1" t="s">
-        <v>1008</v>
       </c>
       <c r="D416" t="s">
         <v>8</v>
@@ -11560,13 +11572,13 @@
     </row>
     <row r="417" spans="1:5">
       <c r="A417" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C417" s="1" t="s">
         <v>1009</v>
-      </c>
-      <c r="B417" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C417" s="1" t="s">
-        <v>1011</v>
       </c>
       <c r="D417" t="s">
         <v>8</v>
@@ -11577,13 +11589,13 @@
     </row>
     <row r="418" spans="1:5">
       <c r="A418" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C418" s="1" t="s">
         <v>1012</v>
-      </c>
-      <c r="B418" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C418" s="1" t="s">
-        <v>1013</v>
       </c>
       <c r="D418" t="s">
         <v>8</v>
@@ -11594,10 +11606,10 @@
     </row>
     <row r="419" spans="1:5">
       <c r="A419" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B419" t="s">
         <v>1014</v>
-      </c>
-      <c r="B419" t="s">
-        <v>1010</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>1015</v>
@@ -11614,10 +11626,10 @@
         <v>1016</v>
       </c>
       <c r="B420" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C420" s="1" t="s">
         <v>1017</v>
-      </c>
-      <c r="C420" s="1" t="s">
-        <v>1018</v>
       </c>
       <c r="D420" t="s">
         <v>8</v>
@@ -11628,13 +11640,13 @@
     </row>
     <row r="421" spans="1:5">
       <c r="A421" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C421" s="1" t="s">
         <v>1019</v>
-      </c>
-      <c r="B421" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C421" s="1" t="s">
-        <v>1020</v>
       </c>
       <c r="D421" t="s">
         <v>8</v>
@@ -11645,30 +11657,30 @@
     </row>
     <row r="422" spans="1:5">
       <c r="A422" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B422" t="s">
         <v>1021</v>
       </c>
-      <c r="B422" t="s">
+      <c r="C422" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="C422" s="1" t="s">
-        <v>1023</v>
-      </c>
       <c r="D422" t="s">
         <v>8</v>
       </c>
       <c r="E422" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423" spans="1:5">
       <c r="A423" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C423" s="1" t="s">
         <v>1024</v>
-      </c>
-      <c r="B423" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C423" s="1" t="s">
-        <v>1026</v>
       </c>
       <c r="D423" t="s">
         <v>8</v>
@@ -11679,13 +11691,13 @@
     </row>
     <row r="424" spans="1:5">
       <c r="A424" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C424" s="1" t="s">
         <v>1027</v>
-      </c>
-      <c r="B424" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C424" s="1" t="s">
-        <v>1028</v>
       </c>
       <c r="D424" t="s">
         <v>8</v>
@@ -11696,10 +11708,10 @@
     </row>
     <row r="425" spans="1:5">
       <c r="A425" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B425" t="s">
         <v>1029</v>
-      </c>
-      <c r="B425" t="s">
-        <v>1025</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>1030</v>
@@ -11708,7 +11720,7 @@
         <v>8</v>
       </c>
       <c r="E425" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -11716,44 +11728,44 @@
         <v>1031</v>
       </c>
       <c r="B426" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C426" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="C426" s="1" t="s">
-        <v>1033</v>
-      </c>
       <c r="D426" t="s">
         <v>8</v>
       </c>
       <c r="E426" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427" spans="1:5">
       <c r="A427" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C427" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="B427" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C427" s="1" t="s">
-        <v>1035</v>
-      </c>
       <c r="D427" t="s">
         <v>8</v>
       </c>
       <c r="E427" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428" spans="1:5">
       <c r="A428" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B428" t="s">
         <v>1036</v>
       </c>
-      <c r="B428" t="s">
+      <c r="C428" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>1038</v>
       </c>
       <c r="D428" t="s">
         <v>8</v>
@@ -11764,13 +11776,13 @@
     </row>
     <row r="429" spans="1:5">
       <c r="A429" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C429" s="1" t="s">
         <v>1039</v>
-      </c>
-      <c r="B429" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C429" s="1" t="s">
-        <v>1041</v>
       </c>
       <c r="D429" t="s">
         <v>8</v>
@@ -11781,30 +11793,30 @@
     </row>
     <row r="430" spans="1:5">
       <c r="A430" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C430" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="B430" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>1043</v>
-      </c>
       <c r="D430" t="s">
         <v>8</v>
       </c>
       <c r="E430" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431" spans="1:5">
       <c r="A431" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B431" t="s">
         <v>1044</v>
       </c>
-      <c r="B431" t="s">
+      <c r="C431" s="1" t="s">
         <v>1045</v>
-      </c>
-      <c r="C431" s="1" t="s">
-        <v>1046</v>
       </c>
       <c r="D431" t="s">
         <v>8</v>
@@ -11815,27 +11827,27 @@
     </row>
     <row r="432" spans="1:5">
       <c r="A432" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C432" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="B432" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C432" s="1" t="s">
-        <v>1048</v>
-      </c>
       <c r="D432" t="s">
         <v>8</v>
       </c>
       <c r="E432" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433" spans="1:5">
       <c r="A433" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B433" t="s">
         <v>1049</v>
-      </c>
-      <c r="B433" t="s">
-        <v>1045</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>1050</v>
@@ -11844,7 +11856,7 @@
         <v>8</v>
       </c>
       <c r="E433" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -11852,10 +11864,10 @@
         <v>1051</v>
       </c>
       <c r="B434" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C434" s="1" t="s">
         <v>1052</v>
-      </c>
-      <c r="C434" s="1" t="s">
-        <v>1053</v>
       </c>
       <c r="D434" t="s">
         <v>8</v>
@@ -11866,13 +11878,13 @@
     </row>
     <row r="435" spans="1:5">
       <c r="A435" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C435" s="1" t="s">
         <v>1054</v>
-      </c>
-      <c r="B435" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C435" s="1" t="s">
-        <v>1055</v>
       </c>
       <c r="D435" t="s">
         <v>8</v>
@@ -11883,10 +11895,10 @@
     </row>
     <row r="436" spans="1:5">
       <c r="A436" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B436" t="s">
         <v>1056</v>
-      </c>
-      <c r="B436" t="s">
-        <v>1052</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>1057</v>
@@ -11895,7 +11907,7 @@
         <v>8</v>
       </c>
       <c r="E436" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -11903,10 +11915,10 @@
         <v>1058</v>
       </c>
       <c r="B437" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C437" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="C437" s="1" t="s">
-        <v>1060</v>
       </c>
       <c r="D437" t="s">
         <v>8</v>
@@ -11917,27 +11929,27 @@
     </row>
     <row r="438" spans="1:5">
       <c r="A438" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C438" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="B438" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>1062</v>
-      </c>
       <c r="D438" t="s">
         <v>8</v>
       </c>
       <c r="E438" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439" spans="1:5">
       <c r="A439" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B439" t="s">
         <v>1063</v>
-      </c>
-      <c r="B439" t="s">
-        <v>1059</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>1064</v>
@@ -11946,7 +11958,7 @@
         <v>8</v>
       </c>
       <c r="E439" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -11954,10 +11966,10 @@
         <v>1065</v>
       </c>
       <c r="B440" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C440" s="1" t="s">
         <v>1066</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>1067</v>
       </c>
       <c r="D440" t="s">
         <v>8</v>
@@ -11968,84 +11980,84 @@
     </row>
     <row r="441" spans="1:5">
       <c r="A441" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C441" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="B441" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C441" s="1" t="s">
-        <v>1070</v>
-      </c>
       <c r="D441" t="s">
         <v>8</v>
       </c>
       <c r="E441" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442" spans="1:5">
       <c r="A442" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C442" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="B442" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>1072</v>
-      </c>
       <c r="D442" t="s">
         <v>8</v>
       </c>
       <c r="E442" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:5">
       <c r="A443" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B443" t="s">
         <v>1073</v>
       </c>
-      <c r="B443" t="s">
+      <c r="C443" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="C443" s="1" t="s">
-        <v>1075</v>
-      </c>
       <c r="D443" t="s">
         <v>8</v>
       </c>
       <c r="E443" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444" spans="1:5">
       <c r="A444" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C444" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="B444" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C444" s="1" t="s">
-        <v>1078</v>
-      </c>
       <c r="D444" t="s">
         <v>8</v>
       </c>
       <c r="E444" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445" spans="1:5">
       <c r="A445" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C445" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="B445" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C445" s="1" t="s">
-        <v>1081</v>
-      </c>
       <c r="D445" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E445" t="b">
         <v>0</v>
@@ -12053,13 +12065,13 @@
     </row>
     <row r="446" spans="1:5">
       <c r="A446" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C446" s="1" t="s">
         <v>1082</v>
-      </c>
-      <c r="B446" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C446" s="1" t="s">
-        <v>1083</v>
       </c>
       <c r="D446" t="s">
         <v>8</v>
@@ -12070,10 +12082,10 @@
     </row>
     <row r="447" spans="1:5">
       <c r="A447" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B447" t="s">
         <v>1084</v>
-      </c>
-      <c r="B447" t="s">
-        <v>1080</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>1085</v>
@@ -12090,7 +12102,7 @@
         <v>1086</v>
       </c>
       <c r="B448" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>1087</v>
@@ -12099,7 +12111,7 @@
         <v>8</v>
       </c>
       <c r="E448" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -12107,13 +12119,13 @@
         <v>1088</v>
       </c>
       <c r="B449" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C449" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="C449" s="1" t="s">
-        <v>1090</v>
-      </c>
       <c r="D449" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E449" t="b">
         <v>0</v>
@@ -12121,27 +12133,27 @@
     </row>
     <row r="450" spans="1:5">
       <c r="A450" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C450" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="B450" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C450" s="1" t="s">
-        <v>1092</v>
-      </c>
       <c r="D450" t="s">
         <v>8</v>
       </c>
       <c r="E450" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451" spans="1:5">
       <c r="A451" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B451" t="s">
         <v>1093</v>
-      </c>
-      <c r="B451" t="s">
-        <v>1089</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>1094</v>
@@ -12150,7 +12162,7 @@
         <v>8</v>
       </c>
       <c r="E451" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -12158,10 +12170,10 @@
         <v>1095</v>
       </c>
       <c r="B452" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C452" s="1" t="s">
         <v>1096</v>
-      </c>
-      <c r="C452" s="1" t="s">
-        <v>1097</v>
       </c>
       <c r="D452" t="s">
         <v>8</v>
@@ -12172,44 +12184,44 @@
     </row>
     <row r="453" spans="1:5">
       <c r="A453" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C453" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="B453" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C453" s="1" t="s">
-        <v>1100</v>
-      </c>
       <c r="D453" t="s">
         <v>8</v>
       </c>
       <c r="E453" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454" spans="1:5">
       <c r="A454" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C454" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="B454" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C454" s="1" t="s">
-        <v>1102</v>
-      </c>
       <c r="D454" t="s">
         <v>8</v>
       </c>
       <c r="E454" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455" spans="1:5">
       <c r="A455" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B455" t="s">
         <v>1103</v>
-      </c>
-      <c r="B455" t="s">
-        <v>1099</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>1104</v>
@@ -12218,7 +12230,7 @@
         <v>8</v>
       </c>
       <c r="E455" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -12226,58 +12238,58 @@
         <v>1105</v>
       </c>
       <c r="B456" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C456" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="C456" s="1" t="s">
-        <v>1107</v>
-      </c>
       <c r="D456" t="s">
         <v>8</v>
       </c>
       <c r="E456" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457" spans="1:5">
       <c r="A457" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C457" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="B457" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C457" s="1" t="s">
-        <v>1110</v>
-      </c>
       <c r="D457" t="s">
         <v>8</v>
       </c>
       <c r="E457" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458" spans="1:5">
       <c r="A458" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C458" s="1" t="s">
         <v>1111</v>
       </c>
-      <c r="B458" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C458" s="1" t="s">
-        <v>1112</v>
-      </c>
       <c r="D458" t="s">
         <v>8</v>
       </c>
       <c r="E458" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459" spans="1:5">
       <c r="A459" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B459" t="s">
         <v>1113</v>
-      </c>
-      <c r="B459" t="s">
-        <v>1109</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>1114</v>
@@ -12294,24 +12306,24 @@
         <v>1115</v>
       </c>
       <c r="B460" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D460" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E460" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461" spans="1:5">
       <c r="A461" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B461" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>1118</v>
@@ -12320,7 +12332,7 @@
         <v>8</v>
       </c>
       <c r="E461" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -12328,13 +12340,13 @@
         <v>1119</v>
       </c>
       <c r="B462" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="D462" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E462" t="b">
         <v>0</v>
@@ -12342,10 +12354,10 @@
     </row>
     <row r="463" spans="1:5">
       <c r="A463" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B463" t="s">
         <v>1121</v>
-      </c>
-      <c r="B463" t="s">
-        <v>1117</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>1122</v>
@@ -12354,7 +12366,7 @@
         <v>8</v>
       </c>
       <c r="E463" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -12362,10 +12374,10 @@
         <v>1123</v>
       </c>
       <c r="B464" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C464" s="1" t="s">
         <v>1124</v>
-      </c>
-      <c r="C464" s="1" t="s">
-        <v>1125</v>
       </c>
       <c r="D464" t="s">
         <v>8</v>
@@ -12376,47 +12388,47 @@
     </row>
     <row r="465" spans="1:5">
       <c r="A465" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C465" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="B465" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C465" s="1" t="s">
-        <v>1128</v>
-      </c>
       <c r="D465" t="s">
         <v>8</v>
       </c>
       <c r="E465" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466" spans="1:5">
       <c r="A466" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C466" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="B466" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C466" s="1" t="s">
-        <v>1130</v>
-      </c>
       <c r="D466" t="s">
         <v>8</v>
       </c>
       <c r="E466" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467" spans="1:5">
       <c r="A467" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B467" t="s">
         <v>1131</v>
       </c>
-      <c r="B467" t="s">
+      <c r="C467" s="1" t="s">
         <v>1132</v>
-      </c>
-      <c r="C467" s="1" t="s">
-        <v>1133</v>
       </c>
       <c r="D467" t="s">
         <v>8</v>
@@ -12427,47 +12439,47 @@
     </row>
     <row r="468" spans="1:5">
       <c r="A468" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C468" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="B468" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C468" s="1" t="s">
-        <v>1135</v>
-      </c>
       <c r="D468" t="s">
         <v>8</v>
       </c>
       <c r="E468" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:5">
       <c r="A469" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B469" t="s">
         <v>1136</v>
       </c>
-      <c r="B469" t="s">
+      <c r="C469" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="C469" s="1" t="s">
-        <v>1138</v>
-      </c>
       <c r="D469" t="s">
         <v>8</v>
       </c>
       <c r="E469" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470" spans="1:5">
       <c r="A470" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C470" s="1" t="s">
         <v>1139</v>
-      </c>
-      <c r="B470" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C470" s="1" t="s">
-        <v>1141</v>
       </c>
       <c r="D470" t="s">
         <v>8</v>
@@ -12478,10 +12490,13 @@
     </row>
     <row r="471" spans="1:5">
       <c r="A471" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C471" s="1" t="s">
         <v>1142</v>
-      </c>
-      <c r="B471" t="s">
-        <v>1140</v>
       </c>
       <c r="D471" t="s">
         <v>8</v>
@@ -12512,10 +12527,7 @@
         <v>1146</v>
       </c>
       <c r="B473" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="D473" t="s">
         <v>8</v>
@@ -12526,13 +12538,13 @@
     </row>
     <row r="474" spans="1:5">
       <c r="A474" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C474" s="1" t="s">
         <v>1149</v>
-      </c>
-      <c r="B474" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C474" s="1" t="s">
-        <v>1150</v>
       </c>
       <c r="D474" t="s">
         <v>8</v>
@@ -12543,13 +12555,13 @@
     </row>
     <row r="475" spans="1:5">
       <c r="A475" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B475" t="s">
         <v>1151</v>
       </c>
-      <c r="B475" t="s">
+      <c r="C475" s="1" t="s">
         <v>1152</v>
-      </c>
-      <c r="C475" s="1" t="s">
-        <v>1153</v>
       </c>
       <c r="D475" t="s">
         <v>8</v>
@@ -12560,13 +12572,13 @@
     </row>
     <row r="476" spans="1:5">
       <c r="A476" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C476" s="1" t="s">
         <v>1154</v>
-      </c>
-      <c r="B476" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C476" s="1" t="s">
-        <v>1156</v>
       </c>
       <c r="D476" t="s">
         <v>8</v>
@@ -12577,64 +12589,64 @@
     </row>
     <row r="477" spans="1:5">
       <c r="A477" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C477" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="B477" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C477" s="1" t="s">
-        <v>1159</v>
-      </c>
       <c r="D477" t="s">
         <v>8</v>
       </c>
       <c r="E477" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478" spans="1:5">
       <c r="A478" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C478" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="B478" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C478" s="1" t="s">
-        <v>1161</v>
-      </c>
       <c r="D478" t="s">
         <v>8</v>
       </c>
       <c r="E478" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479" spans="1:5">
       <c r="A479" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B479" t="s">
         <v>1162</v>
       </c>
-      <c r="B479" t="s">
+      <c r="C479" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="C479" s="1" t="s">
-        <v>1164</v>
-      </c>
       <c r="D479" t="s">
         <v>8</v>
       </c>
       <c r="E479" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480" spans="1:5">
       <c r="A480" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C480" s="1" t="s">
         <v>1165</v>
-      </c>
-      <c r="B480" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C480" s="1" t="s">
-        <v>1167</v>
       </c>
       <c r="D480" t="s">
         <v>8</v>
@@ -12645,13 +12657,13 @@
     </row>
     <row r="481" spans="1:5">
       <c r="A481" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C481" s="1" t="s">
         <v>1168</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C481" s="1" t="s">
-        <v>1170</v>
       </c>
       <c r="D481" t="s">
         <v>8</v>
@@ -12662,13 +12674,13 @@
     </row>
     <row r="482" spans="1:5">
       <c r="A482" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C482" s="1" t="s">
         <v>1171</v>
-      </c>
-      <c r="B482" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C482" s="1" t="s">
-        <v>1173</v>
       </c>
       <c r="D482" t="s">
         <v>8</v>
@@ -12679,27 +12691,27 @@
     </row>
     <row r="483" spans="1:5">
       <c r="A483" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C483" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="B483" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C483" s="1" t="s">
-        <v>1175</v>
-      </c>
       <c r="D483" t="s">
         <v>8</v>
       </c>
       <c r="E483" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="484" spans="1:5">
       <c r="A484" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B484" t="s">
         <v>1176</v>
-      </c>
-      <c r="B484" t="s">
-        <v>1172</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>1177</v>
@@ -12708,7 +12720,7 @@
         <v>8</v>
       </c>
       <c r="E484" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -12716,27 +12728,27 @@
         <v>1178</v>
       </c>
       <c r="B485" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C485" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="C485" s="1" t="s">
-        <v>1180</v>
-      </c>
       <c r="D485" t="s">
         <v>8</v>
       </c>
       <c r="E485" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486" spans="1:5">
       <c r="A486" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C486" s="1" t="s">
         <v>1181</v>
-      </c>
-      <c r="B486" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C486" s="1" t="s">
-        <v>1182</v>
       </c>
       <c r="D486" t="s">
         <v>8</v>
@@ -12747,10 +12759,10 @@
     </row>
     <row r="487" spans="1:5">
       <c r="A487" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B487" t="s">
         <v>1183</v>
-      </c>
-      <c r="B487" t="s">
-        <v>1179</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>1184</v>
@@ -12767,10 +12779,10 @@
         <v>1185</v>
       </c>
       <c r="B488" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C488" s="1" t="s">
         <v>1186</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>1187</v>
       </c>
       <c r="D488" t="s">
         <v>8</v>
@@ -12781,13 +12793,13 @@
     </row>
     <row r="489" spans="1:5">
       <c r="A489" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C489" s="1" t="s">
         <v>1188</v>
-      </c>
-      <c r="B489" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C489" s="1" t="s">
-        <v>1189</v>
       </c>
       <c r="D489" t="s">
         <v>8</v>
@@ -12798,13 +12810,13 @@
     </row>
     <row r="490" spans="1:5">
       <c r="A490" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B490" t="s">
         <v>1190</v>
       </c>
-      <c r="B490" t="s">
+      <c r="C490" s="1" t="s">
         <v>1191</v>
-      </c>
-      <c r="C490" s="1" t="s">
-        <v>1192</v>
       </c>
       <c r="D490" t="s">
         <v>8</v>
@@ -12815,30 +12827,30 @@
     </row>
     <row r="491" spans="1:5">
       <c r="A491" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C491" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="B491" t="s">
-        <v>1194</v>
-      </c>
-      <c r="C491" s="1" t="s">
-        <v>1195</v>
-      </c>
       <c r="D491" t="s">
         <v>8</v>
       </c>
       <c r="E491" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="492" spans="1:5">
       <c r="A492" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C492" s="1" t="s">
         <v>1196</v>
-      </c>
-      <c r="B492" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C492" s="1" t="s">
-        <v>1198</v>
       </c>
       <c r="D492" t="s">
         <v>8</v>
@@ -12849,30 +12861,30 @@
     </row>
     <row r="493" spans="1:5">
       <c r="A493" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C493" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="B493" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C493" s="1" t="s">
-        <v>1201</v>
-      </c>
       <c r="D493" t="s">
         <v>8</v>
       </c>
       <c r="E493" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494" spans="1:5">
       <c r="A494" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C494" s="1" t="s">
         <v>1202</v>
-      </c>
-      <c r="B494" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C494" s="1" t="s">
-        <v>1203</v>
       </c>
       <c r="D494" t="s">
         <v>8</v>
@@ -12883,13 +12895,13 @@
     </row>
     <row r="495" spans="1:5">
       <c r="A495" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B495" t="s">
         <v>1204</v>
       </c>
-      <c r="B495" t="s">
+      <c r="C495" s="1" t="s">
         <v>1205</v>
-      </c>
-      <c r="C495" s="1" t="s">
-        <v>1206</v>
       </c>
       <c r="D495" t="s">
         <v>8</v>
@@ -12900,13 +12912,13 @@
     </row>
     <row r="496" spans="1:5">
       <c r="A496" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C496" s="1" t="s">
         <v>1207</v>
-      </c>
-      <c r="B496" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>1209</v>
       </c>
       <c r="D496" t="s">
         <v>8</v>
@@ -12917,27 +12929,27 @@
     </row>
     <row r="497" spans="1:5">
       <c r="A497" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C497" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="B497" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C497" s="1" t="s">
-        <v>1211</v>
-      </c>
       <c r="D497" t="s">
         <v>8</v>
       </c>
       <c r="E497" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498" spans="1:5">
       <c r="A498" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B498" t="s">
         <v>1212</v>
-      </c>
-      <c r="B498" t="s">
-        <v>1208</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>1213</v>
@@ -12954,7 +12966,7 @@
         <v>1214</v>
       </c>
       <c r="B499" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>1215</v>
@@ -12963,7 +12975,7 @@
         <v>8</v>
       </c>
       <c r="E499" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -12971,10 +12983,10 @@
         <v>1216</v>
       </c>
       <c r="B500" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C500" s="1" t="s">
         <v>1217</v>
-      </c>
-      <c r="C500" s="1" t="s">
-        <v>1218</v>
       </c>
       <c r="D500" t="s">
         <v>8</v>
@@ -12985,13 +12997,13 @@
     </row>
     <row r="501" spans="1:5">
       <c r="A501" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C501" s="1" t="s">
         <v>1219</v>
-      </c>
-      <c r="B501" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C501" s="1" t="s">
-        <v>1221</v>
       </c>
       <c r="D501" t="s">
         <v>8</v>
@@ -13002,13 +13014,13 @@
     </row>
     <row r="502" spans="1:5">
       <c r="A502" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C502" s="1" t="s">
         <v>1222</v>
-      </c>
-      <c r="B502" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C502" s="1" t="s">
-        <v>1224</v>
       </c>
       <c r="D502" t="s">
         <v>8</v>
@@ -13019,13 +13031,13 @@
     </row>
     <row r="503" spans="1:5">
       <c r="A503" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C503" s="1" t="s">
         <v>1225</v>
-      </c>
-      <c r="B503" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>1227</v>
       </c>
       <c r="D503" t="s">
         <v>8</v>
@@ -13036,27 +13048,27 @@
     </row>
     <row r="504" spans="1:5">
       <c r="A504" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C504" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="B504" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C504" s="1" t="s">
-        <v>1229</v>
-      </c>
       <c r="D504" t="s">
         <v>8</v>
       </c>
       <c r="E504" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="505" spans="1:5">
       <c r="A505" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B505" t="s">
         <v>1230</v>
-      </c>
-      <c r="B505" t="s">
-        <v>1226</v>
       </c>
       <c r="C505" s="1" t="s">
         <v>1231</v>
@@ -13065,7 +13077,7 @@
         <v>8</v>
       </c>
       <c r="E505" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="506" spans="1:5">
@@ -13073,7 +13085,7 @@
         <v>1232</v>
       </c>
       <c r="B506" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="C506" s="1" t="s">
         <v>1233</v>
@@ -13082,7 +13094,7 @@
         <v>8</v>
       </c>
       <c r="E506" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507" spans="1:5">
@@ -13090,27 +13102,27 @@
         <v>1234</v>
       </c>
       <c r="B507" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C507" s="1" t="s">
         <v>1235</v>
       </c>
-      <c r="C507" s="1" t="s">
-        <v>1236</v>
-      </c>
       <c r="D507" t="s">
         <v>8</v>
       </c>
       <c r="E507" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508" spans="1:5">
       <c r="A508" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C508" s="1" t="s">
         <v>1237</v>
-      </c>
-      <c r="B508" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C508" s="1" t="s">
-        <v>1238</v>
       </c>
       <c r="D508" t="s">
         <v>8</v>
@@ -13121,13 +13133,13 @@
     </row>
     <row r="509" spans="1:5">
       <c r="A509" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B509" t="s">
         <v>1239</v>
       </c>
-      <c r="B509" t="s">
+      <c r="C509" s="1" t="s">
         <v>1240</v>
-      </c>
-      <c r="C509" s="1" t="s">
-        <v>1241</v>
       </c>
       <c r="D509" t="s">
         <v>8</v>
@@ -13138,33 +13150,33 @@
     </row>
     <row r="510" spans="1:5">
       <c r="A510" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C510" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="B510" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C510" s="1" t="s">
-        <v>1243</v>
-      </c>
       <c r="D510" t="s">
         <v>8</v>
       </c>
       <c r="E510" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="511" spans="1:5">
       <c r="A511" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B511" t="s">
         <v>1244</v>
-      </c>
-      <c r="B511" t="s">
-        <v>1240</v>
       </c>
       <c r="C511" s="1" t="s">
         <v>1245</v>
       </c>
       <c r="D511" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E511" t="b">
         <v>0</v>
@@ -13175,7 +13187,7 @@
         <v>1246</v>
       </c>
       <c r="B512" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="C512" s="1" t="s">
         <v>1247</v>
@@ -13192,16 +13204,16 @@
         <v>1248</v>
       </c>
       <c r="B513" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="C513" s="1" t="s">
         <v>1249</v>
       </c>
       <c r="D513" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E513" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514" spans="1:5">
@@ -13209,47 +13221,47 @@
         <v>1250</v>
       </c>
       <c r="B514" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C514" s="1" t="s">
         <v>1251</v>
       </c>
-      <c r="C514" s="1" t="s">
-        <v>1252</v>
-      </c>
       <c r="D514" t="s">
         <v>8</v>
       </c>
       <c r="E514" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515" spans="1:5">
       <c r="A515" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C515" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="B515" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C515" s="1" t="s">
-        <v>1255</v>
-      </c>
       <c r="D515" t="s">
         <v>8</v>
       </c>
       <c r="E515" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516" spans="1:5">
       <c r="A516" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C516" s="1" t="s">
         <v>1256</v>
       </c>
-      <c r="B516" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C516" s="1" t="s">
-        <v>1257</v>
-      </c>
       <c r="D516" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E516" t="b">
         <v>0</v>
@@ -13257,10 +13269,10 @@
     </row>
     <row r="517" spans="1:5">
       <c r="A517" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B517" t="s">
         <v>1258</v>
-      </c>
-      <c r="B517" t="s">
-        <v>1254</v>
       </c>
       <c r="C517" s="1" t="s">
         <v>1259</v>
@@ -13277,16 +13289,16 @@
         <v>1260</v>
       </c>
       <c r="B518" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="C518" s="1" t="s">
         <v>1261</v>
       </c>
       <c r="D518" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E518" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="519" spans="1:5">
@@ -13294,7 +13306,7 @@
         <v>1262</v>
       </c>
       <c r="B519" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="C519" s="1" t="s">
         <v>1263</v>
@@ -13311,27 +13323,27 @@
         <v>1264</v>
       </c>
       <c r="B520" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C520" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="C520" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="D520" t="s">
         <v>8</v>
       </c>
       <c r="E520" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521" spans="1:5">
       <c r="A521" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C521" s="1" t="s">
         <v>1267</v>
-      </c>
-      <c r="B521" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C521" s="1" t="s">
-        <v>1269</v>
       </c>
       <c r="D521" t="s">
         <v>8</v>
@@ -13342,13 +13354,13 @@
     </row>
     <row r="522" spans="1:5">
       <c r="A522" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C522" s="1" t="s">
         <v>1270</v>
-      </c>
-      <c r="B522" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C522" s="1" t="s">
-        <v>1271</v>
       </c>
       <c r="D522" t="s">
         <v>8</v>
@@ -13359,13 +13371,13 @@
     </row>
     <row r="523" spans="1:5">
       <c r="A523" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B523" t="s">
         <v>1272</v>
       </c>
-      <c r="B523" t="s">
+      <c r="C523" s="1" t="s">
         <v>1273</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>1274</v>
       </c>
       <c r="D523" t="s">
         <v>8</v>
@@ -13376,13 +13388,13 @@
     </row>
     <row r="524" spans="1:5">
       <c r="A524" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C524" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>1277</v>
       </c>
       <c r="D524" t="s">
         <v>8</v>
@@ -13393,13 +13405,13 @@
     </row>
     <row r="525" spans="1:5">
       <c r="A525" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C525" s="1" t="s">
         <v>1278</v>
-      </c>
-      <c r="B525" t="s">
-        <v>1279</v>
-      </c>
-      <c r="C525" s="1" t="s">
-        <v>1280</v>
       </c>
       <c r="D525" t="s">
         <v>8</v>
@@ -13410,13 +13422,13 @@
     </row>
     <row r="526" spans="1:5">
       <c r="A526" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C526" s="1" t="s">
         <v>1281</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C526" s="1" t="s">
-        <v>1283</v>
       </c>
       <c r="D526" t="s">
         <v>8</v>
@@ -13427,13 +13439,13 @@
     </row>
     <row r="527" spans="1:5">
       <c r="A527" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C527" s="1" t="s">
         <v>1284</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C527" s="1" t="s">
-        <v>1286</v>
       </c>
       <c r="D527" t="s">
         <v>8</v>
@@ -13444,13 +13456,13 @@
     </row>
     <row r="528" spans="1:5">
       <c r="A528" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C528" s="1" t="s">
         <v>1287</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C528" s="1" t="s">
-        <v>1289</v>
       </c>
       <c r="D528" t="s">
         <v>8</v>
@@ -13461,13 +13473,13 @@
     </row>
     <row r="529" spans="1:5">
       <c r="A529" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C529" s="1" t="s">
         <v>1290</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C529" s="1" t="s">
-        <v>1291</v>
       </c>
       <c r="D529" t="s">
         <v>8</v>
@@ -13478,10 +13490,10 @@
     </row>
     <row r="530" spans="1:5">
       <c r="A530" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B530" t="s">
         <v>1292</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1288</v>
       </c>
       <c r="C530" s="1" t="s">
         <v>1293</v>
@@ -13498,10 +13510,10 @@
         <v>1294</v>
       </c>
       <c r="B531" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C531" s="1" t="s">
         <v>1295</v>
-      </c>
-      <c r="C531" s="1" t="s">
-        <v>1296</v>
       </c>
       <c r="D531" t="s">
         <v>8</v>
@@ -13512,13 +13524,13 @@
     </row>
     <row r="532" spans="1:5">
       <c r="A532" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C532" s="1" t="s">
         <v>1297</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C532" s="1" t="s">
-        <v>1299</v>
       </c>
       <c r="D532" t="s">
         <v>8</v>
@@ -13529,13 +13541,13 @@
     </row>
     <row r="533" spans="1:5">
       <c r="A533" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C533" s="1" t="s">
         <v>1300</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1301</v>
-      </c>
-      <c r="C533" s="1" t="s">
-        <v>1302</v>
       </c>
       <c r="D533" t="s">
         <v>8</v>
@@ -13546,6 +13558,12 @@
     </row>
     <row r="534" spans="1:5">
       <c r="A534" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C534" s="1" t="s">
         <v>1303</v>
       </c>
       <c r="D534" t="s">
@@ -13559,62 +13577,56 @@
       <c r="A535" t="s">
         <v>1304</v>
       </c>
+      <c r="B535" t="s">
+        <v>1305</v>
+      </c>
       <c r="C535" s="1" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D535" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E535" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="536" spans="1:5">
       <c r="A536" t="s">
-        <v>1306</v>
-      </c>
-      <c r="B536" t="s">
         <v>1307</v>
       </c>
-      <c r="C536" s="1" t="s">
-        <v>1308</v>
-      </c>
       <c r="D536" t="s">
         <v>8</v>
       </c>
       <c r="E536" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:5">
       <c r="A537" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C537" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="B537" t="s">
-        <v>1307</v>
-      </c>
-      <c r="C537" s="1" t="s">
-        <v>1310</v>
-      </c>
       <c r="D537" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E537" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538" spans="1:5">
       <c r="A538" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B538" t="s">
         <v>1311</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1307</v>
       </c>
       <c r="C538" s="1" t="s">
         <v>1312</v>
       </c>
       <c r="D538" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E538" t="b">
         <v>1</v>
@@ -13624,6 +13636,9 @@
       <c r="A539" t="s">
         <v>1313</v>
       </c>
+      <c r="B539" t="s">
+        <v>1311</v>
+      </c>
       <c r="C539" s="1" t="s">
         <v>1314</v>
       </c>
@@ -13639,13 +13654,13 @@
         <v>1315</v>
       </c>
       <c r="B540" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="C540" s="1" t="s">
         <v>1316</v>
       </c>
       <c r="D540" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E540" t="b">
         <v>1</v>
@@ -13655,11 +13670,8 @@
       <c r="A541" t="s">
         <v>1317</v>
       </c>
-      <c r="B541" t="s">
+      <c r="C541" s="1" t="s">
         <v>1318</v>
-      </c>
-      <c r="C541" s="1" t="s">
-        <v>1319</v>
       </c>
       <c r="D541" t="s">
         <v>8</v>
@@ -13670,27 +13682,27 @@
     </row>
     <row r="542" spans="1:5">
       <c r="A542" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C542" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="B542" t="s">
-        <v>1307</v>
-      </c>
-      <c r="C542" s="1" t="s">
-        <v>1321</v>
-      </c>
       <c r="D542" t="s">
         <v>8</v>
       </c>
       <c r="E542" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543" spans="1:5">
       <c r="A543" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B543" t="s">
         <v>1322</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1307</v>
       </c>
       <c r="C543" s="1" t="s">
         <v>1323</v>
@@ -13699,7 +13711,7 @@
         <v>8</v>
       </c>
       <c r="E543" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -13707,7 +13719,7 @@
         <v>1324</v>
       </c>
       <c r="B544" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="C544" s="1" t="s">
         <v>1325</v>
@@ -13716,7 +13728,7 @@
         <v>8</v>
       </c>
       <c r="E544" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545" spans="1:5">
@@ -13724,24 +13736,27 @@
         <v>1326</v>
       </c>
       <c r="B545" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C545" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="C545" s="1" t="s">
-        <v>1328</v>
-      </c>
       <c r="D545" t="s">
         <v>8</v>
       </c>
       <c r="E545" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546" spans="1:5">
       <c r="A546" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C546" s="1" t="s">
         <v>1329</v>
-      </c>
-      <c r="C546" s="1" t="s">
-        <v>1330</v>
       </c>
       <c r="D546" t="s">
         <v>8</v>
@@ -13752,6 +13767,9 @@
     </row>
     <row r="547" spans="1:5">
       <c r="A547" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B547" t="s">
         <v>1331</v>
       </c>
       <c r="C547" s="1" t="s">
@@ -13761,16 +13779,13 @@
         <v>8</v>
       </c>
       <c r="E547" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="548" spans="1:5">
       <c r="A548" t="s">
         <v>1333</v>
       </c>
-      <c r="B548" t="s">
-        <v>1307</v>
-      </c>
       <c r="C548" s="1" t="s">
         <v>1334</v>
       </c>
@@ -13785,59 +13800,56 @@
       <c r="A549" t="s">
         <v>1335</v>
       </c>
-      <c r="B549" t="s">
+      <c r="C549" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="C549" s="1" t="s">
-        <v>1337</v>
-      </c>
       <c r="D549" t="s">
         <v>8</v>
       </c>
       <c r="E549" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550" spans="1:5">
       <c r="A550" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C550" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="B550" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C550" s="1" t="s">
-        <v>1340</v>
-      </c>
       <c r="D550" t="s">
         <v>8</v>
       </c>
       <c r="E550" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551" spans="1:5">
       <c r="A551" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C551" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="B551" t="s">
-        <v>1339</v>
-      </c>
-      <c r="C551" s="1" t="s">
-        <v>1342</v>
-      </c>
       <c r="D551" t="s">
         <v>8</v>
       </c>
       <c r="E551" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="552" spans="1:5">
       <c r="A552" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B552" t="s">
         <v>1343</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1339</v>
       </c>
       <c r="C552" s="1" t="s">
         <v>1344</v>
@@ -13854,7 +13866,7 @@
         <v>1345</v>
       </c>
       <c r="B553" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C553" s="1" t="s">
         <v>1346</v>
@@ -13863,7 +13875,7 @@
         <v>8</v>
       </c>
       <c r="E553" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554" spans="1:5">
@@ -13871,10 +13883,10 @@
         <v>1347</v>
       </c>
       <c r="B554" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C554" s="1" t="s">
         <v>1348</v>
-      </c>
-      <c r="C554" s="1" t="s">
-        <v>1349</v>
       </c>
       <c r="D554" t="s">
         <v>8</v>
@@ -13885,13 +13897,13 @@
     </row>
     <row r="555" spans="1:5">
       <c r="A555" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C555" s="1" t="s">
         <v>1350</v>
-      </c>
-      <c r="B555" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C555" s="1" t="s">
-        <v>1352</v>
       </c>
       <c r="D555" t="s">
         <v>8</v>
@@ -13902,13 +13914,13 @@
     </row>
     <row r="556" spans="1:5">
       <c r="A556" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C556" s="1" t="s">
         <v>1353</v>
-      </c>
-      <c r="B556" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C556" s="1" t="s">
-        <v>1354</v>
       </c>
       <c r="D556" t="s">
         <v>8</v>
@@ -13919,10 +13931,10 @@
     </row>
     <row r="557" spans="1:5">
       <c r="A557" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B557" t="s">
         <v>1355</v>
-      </c>
-      <c r="B557" t="s">
-        <v>1351</v>
       </c>
       <c r="C557" s="1" t="s">
         <v>1356</v>
@@ -13931,7 +13943,7 @@
         <v>8</v>
       </c>
       <c r="E557" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -13939,7 +13951,7 @@
         <v>1357</v>
       </c>
       <c r="B558" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="C558" s="1" t="s">
         <v>1358</v>
@@ -13956,16 +13968,16 @@
         <v>1359</v>
       </c>
       <c r="B559" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="C559" s="1" t="s">
         <v>1360</v>
       </c>
       <c r="D559" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E559" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -13973,41 +13985,41 @@
         <v>1361</v>
       </c>
       <c r="B560" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C560" s="1" t="s">
         <v>1362</v>
       </c>
-      <c r="C560" s="1" t="s">
-        <v>1363</v>
-      </c>
       <c r="D560" t="s">
         <v>8</v>
       </c>
       <c r="E560" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="561" spans="1:5">
       <c r="A561" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C561" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="B561" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C561" s="1" t="s">
-        <v>1365</v>
-      </c>
       <c r="D561" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E561" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="562" spans="1:5">
       <c r="A562" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B562" t="s">
         <v>1366</v>
-      </c>
-      <c r="B562" t="s">
-        <v>1362</v>
       </c>
       <c r="C562" s="1" t="s">
         <v>1367</v>
@@ -14016,7 +14028,7 @@
         <v>8</v>
       </c>
       <c r="E562" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563" spans="1:5">
@@ -14024,7 +14036,7 @@
         <v>1368</v>
       </c>
       <c r="B563" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="C563" s="1" t="s">
         <v>1369</v>
@@ -14033,7 +14045,7 @@
         <v>8</v>
       </c>
       <c r="E563" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564" spans="1:5">
@@ -14041,24 +14053,27 @@
         <v>1370</v>
       </c>
       <c r="B564" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C564" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="C564" s="1" t="s">
-        <v>1372</v>
-      </c>
       <c r="D564" t="s">
         <v>8</v>
       </c>
       <c r="E564" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="565" spans="1:5">
       <c r="A565" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C565" s="1" t="s">
         <v>1373</v>
-      </c>
-      <c r="B565" t="s">
-        <v>1371</v>
       </c>
       <c r="D565" t="s">
         <v>8</v>
@@ -14072,32 +14087,63 @@
         <v>1374</v>
       </c>
       <c r="B566" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="D566" t="s">
         <v>8</v>
       </c>
       <c r="E566" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567" spans="1:5">
       <c r="A567" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B567" t="s">
-        <v>1377</v>
-      </c>
-      <c r="C567" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D567" t="s">
+        <v>8</v>
+      </c>
+      <c r="E567" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5">
+      <c r="A568" t="s">
         <v>1378</v>
       </c>
-      <c r="D567" t="s">
-        <v>8</v>
-      </c>
-      <c r="E567" t="b">
+      <c r="B568" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C568" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D568" t="s">
+        <v>8</v>
+      </c>
+      <c r="E568" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5">
+      <c r="A569" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C569" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D569" t="s">
+        <v>8</v>
+      </c>
+      <c r="E569" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14414,8 +14460,8 @@
     <hyperlink ref="C312" r:id="rId309"/>
     <hyperlink ref="C313" r:id="rId310"/>
     <hyperlink ref="C314" r:id="rId311"/>
-    <hyperlink ref="C316" r:id="rId312"/>
-    <hyperlink ref="C317" r:id="rId313"/>
+    <hyperlink ref="C315" r:id="rId312"/>
+    <hyperlink ref="C316" r:id="rId313"/>
     <hyperlink ref="C318" r:id="rId314"/>
     <hyperlink ref="C319" r:id="rId315"/>
     <hyperlink ref="C320" r:id="rId316"/>
@@ -14439,8 +14485,8 @@
     <hyperlink ref="C338" r:id="rId334"/>
     <hyperlink ref="C339" r:id="rId335"/>
     <hyperlink ref="C340" r:id="rId336"/>
-    <hyperlink ref="C342" r:id="rId337"/>
-    <hyperlink ref="C343" r:id="rId338"/>
+    <hyperlink ref="C341" r:id="rId337"/>
+    <hyperlink ref="C342" r:id="rId338"/>
     <hyperlink ref="C344" r:id="rId339"/>
     <hyperlink ref="C345" r:id="rId340"/>
     <hyperlink ref="C346" r:id="rId341"/>
@@ -14568,8 +14614,8 @@
     <hyperlink ref="C468" r:id="rId463"/>
     <hyperlink ref="C469" r:id="rId464"/>
     <hyperlink ref="C470" r:id="rId465"/>
-    <hyperlink ref="C472" r:id="rId466"/>
-    <hyperlink ref="C473" r:id="rId467"/>
+    <hyperlink ref="C471" r:id="rId466"/>
+    <hyperlink ref="C472" r:id="rId467"/>
     <hyperlink ref="C474" r:id="rId468"/>
     <hyperlink ref="C475" r:id="rId469"/>
     <hyperlink ref="C476" r:id="rId470"/>
@@ -14590,9 +14636,9 @@
     <hyperlink ref="C491" r:id="rId485"/>
     <hyperlink ref="C492" r:id="rId486"/>
     <hyperlink ref="C493" r:id="rId487"/>
-    <hyperlink ref="C494" r:id="rId488" location="/recherche-pm"/>
+    <hyperlink ref="C494" r:id="rId488"/>
     <hyperlink ref="C495" r:id="rId489"/>
-    <hyperlink ref="C496" r:id="rId490"/>
+    <hyperlink ref="C496" r:id="rId490" location="/recherche-pm"/>
     <hyperlink ref="C497" r:id="rId491"/>
     <hyperlink ref="C498" r:id="rId492"/>
     <hyperlink ref="C499" r:id="rId493"/>
@@ -14630,8 +14676,8 @@
     <hyperlink ref="C531" r:id="rId525"/>
     <hyperlink ref="C532" r:id="rId526"/>
     <hyperlink ref="C533" r:id="rId527"/>
-    <hyperlink ref="C535" r:id="rId528"/>
-    <hyperlink ref="C536" r:id="rId529"/>
+    <hyperlink ref="C534" r:id="rId528"/>
+    <hyperlink ref="C535" r:id="rId529"/>
     <hyperlink ref="C537" r:id="rId530"/>
     <hyperlink ref="C538" r:id="rId531"/>
     <hyperlink ref="C539" r:id="rId532"/>
@@ -14660,8 +14706,10 @@
     <hyperlink ref="C562" r:id="rId555"/>
     <hyperlink ref="C563" r:id="rId556"/>
     <hyperlink ref="C564" r:id="rId557"/>
-    <hyperlink ref="C566" r:id="rId558"/>
-    <hyperlink ref="C567" r:id="rId559"/>
+    <hyperlink ref="C565" r:id="rId558"/>
+    <hyperlink ref="C566" r:id="rId559"/>
+    <hyperlink ref="C568" r:id="rId560"/>
+    <hyperlink ref="C569" r:id="rId561"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
